--- a/assets/downloads/game-c/Database90Projects.xlsx
+++ b/assets/downloads/game-c/Database90Projects.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30015"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://etsmtl365-my.sharepoint.com/personal/sion-israel_sion_1_ens_etsmtl_ca/Documents/Documents/Working/SIMSE/New Game/Model 2c/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://etsmtl365-my.sharepoint.com/personal/sion-israel_sion_1_ens_etsmtl_ca/Documents/SimSE/SIMSE 17/Official Game/Game C - Estimation &amp; Statistical Regression Analysis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{58FED585-7539-4957-B847-33D684AB86A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="613" documentId="8_{442BE2B5-AA1A-408B-9792-F60A90F9BB77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2D197ADC-A25F-44A5-A611-936A5A7FB059}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B96840B6-E96A-DD4F-B911-7A987F387927}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{B96840B6-E96A-DD4F-B911-7A987F387927}"/>
   </bookViews>
   <sheets>
     <sheet name="Database" sheetId="1" r:id="rId1"/>
@@ -493,7 +493,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -583,6 +583,19 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1464,13 +1477,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6AA8ADD4-30F6-F545-BD96-AFAF9C533433}">
   <dimension ref="A1:M128"/>
-  <sheetFormatPr defaultColWidth="21.625" defaultRowHeight="15.95"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="21.58203125" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="7" style="3" customWidth="1"/>
-    <col min="2" max="5" width="21.625" style="3"/>
-    <col min="6" max="7" width="12.875" style="3" customWidth="1"/>
+    <col min="2" max="5" width="21.58203125" style="3"/>
+    <col min="6" max="7" width="12.83203125" style="3" customWidth="1"/>
     <col min="8" max="12" width="25" style="3" customWidth="1"/>
-    <col min="13" max="16384" width="21.625" style="3"/>
+    <col min="13" max="16384" width="21.58203125" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
@@ -1495,6 +1508,12 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="H1" s="41"/>
+      <c r="I1" s="41"/>
+      <c r="J1" s="41"/>
+      <c r="K1" s="41"/>
+      <c r="L1" s="41"/>
+      <c r="M1" s="41"/>
     </row>
     <row r="2" spans="1:13">
       <c r="A2" s="4">
@@ -1518,12 +1537,12 @@
       <c r="G2" s="6">
         <v>118</v>
       </c>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
-      <c r="J2" s="4"/>
-      <c r="K2" s="4"/>
-      <c r="L2" s="4"/>
-      <c r="M2" s="5"/>
+      <c r="H2" s="42"/>
+      <c r="I2" s="42"/>
+      <c r="J2" s="42"/>
+      <c r="K2" s="42"/>
+      <c r="L2" s="42"/>
+      <c r="M2" s="43"/>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="4">
@@ -1547,12 +1566,12 @@
       <c r="G3" s="6">
         <v>42</v>
       </c>
-      <c r="H3" s="4"/>
-      <c r="I3" s="4"/>
-      <c r="J3" s="4"/>
-      <c r="K3" s="4"/>
-      <c r="L3" s="4"/>
-      <c r="M3" s="5"/>
+      <c r="H3" s="42"/>
+      <c r="I3" s="42"/>
+      <c r="J3" s="42"/>
+      <c r="K3" s="42"/>
+      <c r="L3" s="42"/>
+      <c r="M3" s="43"/>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="4">
@@ -1576,12 +1595,12 @@
       <c r="G4" s="6">
         <v>150</v>
       </c>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4"/>
-      <c r="K4" s="4"/>
-      <c r="L4" s="4"/>
-      <c r="M4" s="5"/>
+      <c r="H4" s="42"/>
+      <c r="I4" s="42"/>
+      <c r="J4" s="42"/>
+      <c r="K4" s="42"/>
+      <c r="L4" s="42"/>
+      <c r="M4" s="43"/>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="4">
@@ -1605,12 +1624,12 @@
       <c r="G5" s="6">
         <v>68</v>
       </c>
-      <c r="H5" s="4"/>
-      <c r="I5" s="4"/>
-      <c r="J5" s="4"/>
-      <c r="K5" s="4"/>
-      <c r="L5" s="4"/>
-      <c r="M5" s="5"/>
+      <c r="H5" s="42"/>
+      <c r="I5" s="42"/>
+      <c r="J5" s="42"/>
+      <c r="K5" s="42"/>
+      <c r="L5" s="42"/>
+      <c r="M5" s="43"/>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="4">
@@ -1634,12 +1653,12 @@
       <c r="G6" s="6">
         <v>1009</v>
       </c>
-      <c r="H6" s="4"/>
-      <c r="I6" s="4"/>
-      <c r="J6" s="4"/>
-      <c r="K6" s="4"/>
-      <c r="L6" s="4"/>
-      <c r="M6" s="5"/>
+      <c r="H6" s="42"/>
+      <c r="I6" s="42"/>
+      <c r="J6" s="42"/>
+      <c r="K6" s="42"/>
+      <c r="L6" s="42"/>
+      <c r="M6" s="43"/>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="4">
@@ -1663,12 +1682,12 @@
       <c r="G7" s="6">
         <v>52</v>
       </c>
-      <c r="H7" s="4"/>
-      <c r="I7" s="4"/>
-      <c r="J7" s="4"/>
-      <c r="K7" s="4"/>
-      <c r="L7" s="4"/>
-      <c r="M7" s="5"/>
+      <c r="H7" s="42"/>
+      <c r="I7" s="42"/>
+      <c r="J7" s="42"/>
+      <c r="K7" s="42"/>
+      <c r="L7" s="42"/>
+      <c r="M7" s="43"/>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="4">
@@ -1692,12 +1711,12 @@
       <c r="G8" s="5">
         <v>274.09199999999998</v>
       </c>
-      <c r="H8" s="4"/>
-      <c r="I8" s="4"/>
-      <c r="J8" s="4"/>
-      <c r="K8" s="4"/>
-      <c r="L8" s="4"/>
-      <c r="M8" s="5"/>
+      <c r="H8" s="42"/>
+      <c r="I8" s="42"/>
+      <c r="J8" s="42"/>
+      <c r="K8" s="42"/>
+      <c r="L8" s="42"/>
+      <c r="M8" s="43"/>
     </row>
     <row r="9" spans="1:13">
       <c r="A9" s="4">
@@ -1721,12 +1740,12 @@
       <c r="G9" s="5">
         <v>336.84199999999998</v>
       </c>
-      <c r="H9" s="4"/>
-      <c r="I9" s="4"/>
-      <c r="J9" s="4"/>
-      <c r="K9" s="4"/>
-      <c r="L9" s="4"/>
-      <c r="M9" s="5"/>
+      <c r="H9" s="42"/>
+      <c r="I9" s="42"/>
+      <c r="J9" s="42"/>
+      <c r="K9" s="42"/>
+      <c r="L9" s="42"/>
+      <c r="M9" s="43"/>
     </row>
     <row r="10" spans="1:13">
       <c r="A10" s="4">
@@ -1750,12 +1769,12 @@
       <c r="G10" s="6">
         <v>139</v>
       </c>
-      <c r="H10" s="4"/>
-      <c r="I10" s="4"/>
-      <c r="J10" s="4"/>
-      <c r="K10" s="4"/>
-      <c r="L10" s="4"/>
-      <c r="M10" s="5"/>
+      <c r="H10" s="42"/>
+      <c r="I10" s="42"/>
+      <c r="J10" s="42"/>
+      <c r="K10" s="42"/>
+      <c r="L10" s="42"/>
+      <c r="M10" s="43"/>
     </row>
     <row r="11" spans="1:13">
       <c r="A11" s="4">
@@ -1779,12 +1798,12 @@
       <c r="G11" s="5">
         <v>512.04</v>
       </c>
-      <c r="H11" s="4"/>
-      <c r="I11" s="4"/>
-      <c r="J11" s="4"/>
-      <c r="K11" s="4"/>
-      <c r="L11" s="4"/>
-      <c r="M11" s="5"/>
+      <c r="H11" s="42"/>
+      <c r="I11" s="42"/>
+      <c r="J11" s="42"/>
+      <c r="K11" s="42"/>
+      <c r="L11" s="42"/>
+      <c r="M11" s="43"/>
     </row>
     <row r="12" spans="1:13">
       <c r="A12" s="4">
@@ -1808,12 +1827,12 @@
       <c r="G12" s="6">
         <v>12702</v>
       </c>
-      <c r="H12" s="4"/>
-      <c r="I12" s="4"/>
-      <c r="J12" s="4"/>
-      <c r="K12" s="4"/>
-      <c r="L12" s="4"/>
-      <c r="M12" s="5"/>
+      <c r="H12" s="42"/>
+      <c r="I12" s="42"/>
+      <c r="J12" s="42"/>
+      <c r="K12" s="42"/>
+      <c r="L12" s="42"/>
+      <c r="M12" s="43"/>
     </row>
     <row r="13" spans="1:13">
       <c r="A13" s="4">
@@ -1837,12 +1856,12 @@
       <c r="G13" s="5">
         <v>379.512</v>
       </c>
-      <c r="H13" s="4"/>
-      <c r="I13" s="4"/>
-      <c r="J13" s="4"/>
-      <c r="K13" s="4"/>
-      <c r="L13" s="4"/>
-      <c r="M13" s="5"/>
+      <c r="H13" s="42"/>
+      <c r="I13" s="42"/>
+      <c r="J13" s="42"/>
+      <c r="K13" s="42"/>
+      <c r="L13" s="42"/>
+      <c r="M13" s="43"/>
     </row>
     <row r="14" spans="1:13">
       <c r="A14" s="4">
@@ -1866,12 +1885,12 @@
       <c r="G14" s="5">
         <v>397.58399999999995</v>
       </c>
-      <c r="H14" s="4"/>
-      <c r="I14" s="4"/>
-      <c r="J14" s="4"/>
-      <c r="K14" s="4"/>
-      <c r="L14" s="4"/>
-      <c r="M14" s="5"/>
+      <c r="H14" s="42"/>
+      <c r="I14" s="42"/>
+      <c r="J14" s="42"/>
+      <c r="K14" s="42"/>
+      <c r="L14" s="42"/>
+      <c r="M14" s="43"/>
     </row>
     <row r="15" spans="1:13">
       <c r="A15" s="4">
@@ -1895,12 +1914,12 @@
       <c r="G15" s="5">
         <v>659.62799999999993</v>
       </c>
-      <c r="H15" s="4"/>
-      <c r="I15" s="4"/>
-      <c r="J15" s="4"/>
-      <c r="K15" s="4"/>
-      <c r="L15" s="4"/>
-      <c r="M15" s="5"/>
+      <c r="H15" s="42"/>
+      <c r="I15" s="42"/>
+      <c r="J15" s="42"/>
+      <c r="K15" s="42"/>
+      <c r="L15" s="42"/>
+      <c r="M15" s="43"/>
     </row>
     <row r="16" spans="1:13">
       <c r="A16" s="4">
@@ -1924,12 +1943,12 @@
       <c r="G16" s="5">
         <v>482.92399999999998</v>
       </c>
-      <c r="H16" s="4"/>
-      <c r="I16" s="4"/>
-      <c r="J16" s="4"/>
-      <c r="K16" s="4"/>
-      <c r="L16" s="4"/>
-      <c r="M16" s="5"/>
+      <c r="H16" s="42"/>
+      <c r="I16" s="42"/>
+      <c r="J16" s="42"/>
+      <c r="K16" s="42"/>
+      <c r="L16" s="42"/>
+      <c r="M16" s="43"/>
     </row>
     <row r="17" spans="1:13">
       <c r="A17" s="4">
@@ -1953,12 +1972,12 @@
       <c r="G17" s="6">
         <v>110</v>
       </c>
-      <c r="H17" s="4"/>
-      <c r="I17" s="4"/>
-      <c r="J17" s="4"/>
-      <c r="K17" s="4"/>
-      <c r="L17" s="4"/>
-      <c r="M17" s="5"/>
+      <c r="H17" s="42"/>
+      <c r="I17" s="42"/>
+      <c r="J17" s="42"/>
+      <c r="K17" s="42"/>
+      <c r="L17" s="42"/>
+      <c r="M17" s="43"/>
     </row>
     <row r="18" spans="1:13">
       <c r="A18" s="4">
@@ -1982,12 +2001,12 @@
       <c r="G18" s="6">
         <v>1100</v>
       </c>
-      <c r="H18" s="4"/>
-      <c r="I18" s="4"/>
-      <c r="J18" s="4"/>
-      <c r="K18" s="4"/>
-      <c r="L18" s="4"/>
-      <c r="M18" s="5"/>
+      <c r="H18" s="42"/>
+      <c r="I18" s="42"/>
+      <c r="J18" s="42"/>
+      <c r="K18" s="42"/>
+      <c r="L18" s="42"/>
+      <c r="M18" s="43"/>
     </row>
     <row r="19" spans="1:13">
       <c r="A19" s="4">
@@ -2011,12 +2030,12 @@
       <c r="G19" s="6">
         <v>142</v>
       </c>
-      <c r="H19" s="4"/>
-      <c r="I19" s="4"/>
-      <c r="J19" s="4"/>
-      <c r="K19" s="4"/>
-      <c r="L19" s="4"/>
-      <c r="M19" s="5"/>
+      <c r="H19" s="42"/>
+      <c r="I19" s="42"/>
+      <c r="J19" s="42"/>
+      <c r="K19" s="42"/>
+      <c r="L19" s="42"/>
+      <c r="M19" s="43"/>
     </row>
     <row r="20" spans="1:13">
       <c r="A20" s="4">
@@ -2040,12 +2059,12 @@
       <c r="G20" s="5">
         <v>475.89599999999996</v>
       </c>
-      <c r="H20" s="4"/>
-      <c r="I20" s="4"/>
-      <c r="J20" s="4"/>
-      <c r="K20" s="4"/>
-      <c r="L20" s="4"/>
-      <c r="M20" s="5"/>
+      <c r="H20" s="42"/>
+      <c r="I20" s="42"/>
+      <c r="J20" s="42"/>
+      <c r="K20" s="42"/>
+      <c r="L20" s="42"/>
+      <c r="M20" s="43"/>
     </row>
     <row r="21" spans="1:13">
       <c r="A21" s="4">
@@ -2069,12 +2088,12 @@
       <c r="G21" s="4">
         <v>260</v>
       </c>
-      <c r="H21" s="4"/>
-      <c r="I21" s="4"/>
-      <c r="J21" s="4"/>
-      <c r="K21" s="4"/>
-      <c r="L21" s="4"/>
-      <c r="M21" s="5"/>
+      <c r="H21" s="42"/>
+      <c r="I21" s="42"/>
+      <c r="J21" s="42"/>
+      <c r="K21" s="42"/>
+      <c r="L21" s="42"/>
+      <c r="M21" s="43"/>
     </row>
     <row r="22" spans="1:13">
       <c r="A22" s="4">
@@ -2098,12 +2117,12 @@
       <c r="G22" s="6">
         <v>2879</v>
       </c>
-      <c r="H22" s="4"/>
-      <c r="I22" s="4"/>
-      <c r="J22" s="4"/>
-      <c r="K22" s="4"/>
-      <c r="L22" s="4"/>
-      <c r="M22" s="5"/>
+      <c r="H22" s="42"/>
+      <c r="I22" s="42"/>
+      <c r="J22" s="42"/>
+      <c r="K22" s="42"/>
+      <c r="L22" s="42"/>
+      <c r="M22" s="43"/>
     </row>
     <row r="23" spans="1:13">
       <c r="A23" s="4">
@@ -2127,12 +2146,12 @@
       <c r="G23" s="6">
         <v>190</v>
       </c>
-      <c r="H23" s="4"/>
-      <c r="I23" s="4"/>
-      <c r="J23" s="4"/>
-      <c r="K23" s="4"/>
-      <c r="L23" s="4"/>
-      <c r="M23" s="5"/>
+      <c r="H23" s="42"/>
+      <c r="I23" s="42"/>
+      <c r="J23" s="42"/>
+      <c r="K23" s="42"/>
+      <c r="L23" s="42"/>
+      <c r="M23" s="43"/>
     </row>
     <row r="24" spans="1:13">
       <c r="A24" s="4">
@@ -2156,12 +2175,12 @@
       <c r="G24" s="5">
         <v>691.25399999999991</v>
       </c>
-      <c r="H24" s="4"/>
-      <c r="I24" s="4"/>
-      <c r="J24" s="4"/>
-      <c r="K24" s="4"/>
-      <c r="L24" s="4"/>
-      <c r="M24" s="5"/>
+      <c r="H24" s="42"/>
+      <c r="I24" s="42"/>
+      <c r="J24" s="42"/>
+      <c r="K24" s="42"/>
+      <c r="L24" s="42"/>
+      <c r="M24" s="43"/>
     </row>
     <row r="25" spans="1:13">
       <c r="A25" s="4">
@@ -2185,12 +2204,12 @@
       <c r="G25" s="5">
         <v>466.6592</v>
       </c>
-      <c r="H25" s="4"/>
-      <c r="I25" s="4"/>
-      <c r="J25" s="4"/>
-      <c r="K25" s="4"/>
-      <c r="L25" s="6"/>
-      <c r="M25" s="6"/>
+      <c r="H25" s="42"/>
+      <c r="I25" s="42"/>
+      <c r="J25" s="42"/>
+      <c r="K25" s="42"/>
+      <c r="L25" s="44"/>
+      <c r="M25" s="44"/>
     </row>
     <row r="26" spans="1:13">
       <c r="A26" s="4">
@@ -2214,12 +2233,12 @@
       <c r="G26" s="6">
         <v>855</v>
       </c>
-      <c r="H26" s="4"/>
-      <c r="I26" s="1"/>
-      <c r="J26" s="4"/>
-      <c r="K26" s="4"/>
-      <c r="L26" s="4"/>
-      <c r="M26" s="5"/>
+      <c r="H26" s="42"/>
+      <c r="I26" s="45"/>
+      <c r="J26" s="42"/>
+      <c r="K26" s="42"/>
+      <c r="L26" s="42"/>
+      <c r="M26" s="43"/>
     </row>
     <row r="27" spans="1:13">
       <c r="A27" s="4">
@@ -2243,12 +2262,12 @@
       <c r="G27" s="5">
         <v>421.67999999999995</v>
       </c>
-      <c r="H27" s="4"/>
-      <c r="I27" s="1"/>
-      <c r="J27" s="4"/>
-      <c r="K27" s="4"/>
-      <c r="L27" s="4"/>
-      <c r="M27" s="5"/>
+      <c r="H27" s="42"/>
+      <c r="I27" s="45"/>
+      <c r="J27" s="42"/>
+      <c r="K27" s="42"/>
+      <c r="L27" s="42"/>
+      <c r="M27" s="43"/>
     </row>
     <row r="28" spans="1:13">
       <c r="A28" s="4">
@@ -2272,12 +2291,12 @@
       <c r="G28" s="5">
         <v>725.39</v>
       </c>
-      <c r="H28" s="4"/>
-      <c r="I28" s="1"/>
-      <c r="J28" s="4"/>
-      <c r="K28" s="4"/>
-      <c r="L28" s="4"/>
-      <c r="M28" s="5"/>
+      <c r="H28" s="42"/>
+      <c r="I28" s="45"/>
+      <c r="J28" s="42"/>
+      <c r="K28" s="42"/>
+      <c r="L28" s="42"/>
+      <c r="M28" s="43"/>
     </row>
     <row r="29" spans="1:13">
       <c r="A29" s="4">
@@ -2301,12 +2320,12 @@
       <c r="G29" s="6">
         <v>170</v>
       </c>
-      <c r="H29" s="4"/>
-      <c r="I29" s="4"/>
-      <c r="J29" s="4"/>
-      <c r="K29" s="4"/>
-      <c r="L29" s="6"/>
-      <c r="M29" s="6"/>
+      <c r="H29" s="42"/>
+      <c r="I29" s="42"/>
+      <c r="J29" s="42"/>
+      <c r="K29" s="42"/>
+      <c r="L29" s="44"/>
+      <c r="M29" s="44"/>
     </row>
     <row r="30" spans="1:13">
       <c r="A30" s="4">
@@ -2330,12 +2349,12 @@
       <c r="G30" s="6">
         <v>189</v>
       </c>
-      <c r="H30" s="4"/>
-      <c r="I30" s="4"/>
-      <c r="J30" s="4"/>
-      <c r="K30" s="4"/>
-      <c r="L30" s="4"/>
-      <c r="M30" s="5"/>
+      <c r="H30" s="42"/>
+      <c r="I30" s="42"/>
+      <c r="J30" s="42"/>
+      <c r="K30" s="42"/>
+      <c r="L30" s="42"/>
+      <c r="M30" s="43"/>
     </row>
     <row r="31" spans="1:13">
       <c r="A31" s="4">
@@ -2359,12 +2378,12 @@
       <c r="G31" s="5">
         <v>406.61999999999995</v>
       </c>
-      <c r="H31" s="4"/>
-      <c r="I31" s="4"/>
-      <c r="J31" s="4"/>
-      <c r="K31" s="4"/>
-      <c r="L31" s="4"/>
-      <c r="M31" s="5"/>
+      <c r="H31" s="42"/>
+      <c r="I31" s="42"/>
+      <c r="J31" s="42"/>
+      <c r="K31" s="42"/>
+      <c r="L31" s="42"/>
+      <c r="M31" s="43"/>
     </row>
     <row r="32" spans="1:13">
       <c r="A32" s="4">
@@ -2388,12 +2407,12 @@
       <c r="G32" s="6">
         <v>195</v>
       </c>
-      <c r="H32" s="4"/>
-      <c r="I32" s="4"/>
-      <c r="J32" s="4"/>
-      <c r="K32" s="4"/>
-      <c r="L32" s="4"/>
-      <c r="M32" s="5"/>
+      <c r="H32" s="42"/>
+      <c r="I32" s="42"/>
+      <c r="J32" s="42"/>
+      <c r="K32" s="42"/>
+      <c r="L32" s="42"/>
+      <c r="M32" s="43"/>
     </row>
     <row r="33" spans="1:7">
       <c r="A33" s="4">
@@ -3931,10 +3950,10 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D74D9E4-2252-9048-8906-C3128104D8BB}">
-  <dimension ref="A1:K175"/>
-  <sheetFormatPr defaultColWidth="10.625" defaultRowHeight="15.95"/>
+  <dimension ref="A1:K166"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.58203125" defaultRowHeight="16"/>
   <sheetData>
-    <row r="1" spans="1:7" ht="32.1">
+    <row r="1" spans="1:7" ht="32">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4422,12 +4441,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="20.100000000000001">
+    <row r="25" spans="1:7" ht="20">
       <c r="A25" s="13" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="16.5">
+    <row r="26" spans="1:7" ht="17">
       <c r="A26" s="14" t="s">
         <v>20</v>
       </c>
@@ -4450,7 +4469,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="16.5">
+    <row r="27" spans="1:7" ht="17">
       <c r="A27" s="14" t="s">
         <v>5</v>
       </c>
@@ -4473,12 +4492,12 @@
         <v>169</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="20.100000000000001">
+    <row r="30" spans="1:7" ht="20">
       <c r="A30" s="13" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="16.5">
+    <row r="31" spans="1:7" ht="17">
       <c r="A31" s="14" t="s">
         <v>20</v>
       </c>
@@ -4501,7 +4520,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="16.5">
+    <row r="32" spans="1:7" ht="17">
       <c r="A32" s="14" t="s">
         <v>6</v>
       </c>
@@ -4529,12 +4548,12 @@
         <v>28</v>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="20.100000000000001">
+    <row r="35" spans="1:7" ht="20">
       <c r="A35" s="13" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="17.100000000000001">
+    <row r="36" spans="1:7" ht="17">
       <c r="A36" s="14" t="s">
         <v>30</v>
       </c>
@@ -4546,7 +4565,7 @@
       <c r="E36" s="14"/>
       <c r="F36" s="14"/>
     </row>
-    <row r="37" spans="1:7" ht="17.100000000000001">
+    <row r="37" spans="1:7" ht="17">
       <c r="A37" s="14">
         <v>9</v>
       </c>
@@ -4558,10 +4577,10 @@
       <c r="E37" s="14"/>
       <c r="F37" s="14"/>
     </row>
-    <row r="38" spans="1:7" ht="17.100000000000001">
+    <row r="38" spans="1:7" ht="17">
       <c r="A38" s="16"/>
     </row>
-    <row r="40" spans="1:7" ht="32.1">
+    <row r="40" spans="1:7" ht="32">
       <c r="A40" s="1" t="s">
         <v>0</v>
       </c>
@@ -5047,7 +5066,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="63" spans="1:8" ht="32.1">
+    <row r="63" spans="1:8" ht="32">
       <c r="A63" s="1" t="s">
         <v>0</v>
       </c>
@@ -5520,7 +5539,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="87" spans="1:7" ht="20.100000000000001">
+    <row r="87" spans="1:7" ht="20">
       <c r="A87" s="10" t="s">
         <v>33</v>
       </c>
@@ -5528,7 +5547,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="88" spans="1:7" ht="20.100000000000001">
+    <row r="88" spans="1:7" ht="20">
       <c r="A88" s="33">
         <v>19</v>
       </c>
@@ -5536,7 +5555,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="89" spans="1:7" ht="20.100000000000001">
+    <row r="89" spans="1:7" ht="20">
       <c r="A89" s="10" t="s">
         <v>76</v>
       </c>
@@ -5544,7 +5563,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="90" spans="1:7" ht="20.100000000000001">
+    <row r="90" spans="1:7" ht="20">
       <c r="A90" s="10">
         <v>1</v>
       </c>
@@ -5552,7 +5571,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:7" ht="20.100000000000001">
+    <row r="91" spans="1:7" ht="20">
       <c r="A91" s="10" t="s">
         <v>34</v>
       </c>
@@ -5560,7 +5579,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="92" spans="1:7" ht="20.100000000000001">
+    <row r="92" spans="1:7" ht="20">
       <c r="A92" s="10" t="s">
         <v>0</v>
       </c>
@@ -5568,7 +5587,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:7" ht="20.100000000000001">
+    <row r="93" spans="1:7" ht="20">
       <c r="A93" s="10"/>
       <c r="D93" s="10"/>
     </row>
@@ -5577,41 +5596,27 @@
         <v>81</v>
       </c>
     </row>
-    <row r="96" spans="1:7" ht="15.75"/>
-    <row r="97" spans="1:1" ht="15.75"/>
-    <row r="98" spans="1:1" ht="15.75"/>
-    <row r="99" spans="1:1" ht="15.75"/>
-    <row r="100" spans="1:1" ht="15.75"/>
-    <row r="104" spans="1:1" ht="15.75"/>
-    <row r="105" spans="1:1" ht="15.75"/>
-    <row r="106" spans="1:1" ht="15.75"/>
-    <row r="107" spans="1:1" ht="15.75"/>
-    <row r="108" spans="1:1" ht="15.75"/>
-    <row r="109" spans="1:1" ht="15.75"/>
-    <row r="110" spans="1:1" ht="15.75"/>
-    <row r="111" spans="1:1" ht="15.75"/>
-    <row r="112" spans="1:1" ht="20.25">
+    <row r="112" spans="1:1" ht="20">
       <c r="A112" s="13" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="113" spans="1:11" ht="16.5">
+    <row r="113" spans="1:11" ht="17">
       <c r="A113" s="14" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="114" spans="1:11" ht="16.5">
+    <row r="114" spans="1:11" ht="17">
       <c r="A114" s="15">
         <v>0.69010000000000005</v>
       </c>
     </row>
-    <row r="115" spans="1:11" ht="15.75"/>
-    <row r="116" spans="1:11" ht="20.25">
+    <row r="116" spans="1:11" ht="20">
       <c r="A116" s="13" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="117" spans="1:11" ht="16.5">
+    <row r="117" spans="1:11" ht="17">
       <c r="A117" s="14" t="s">
         <v>86</v>
       </c>
@@ -5621,7 +5626,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="121" spans="1:11" ht="32.1">
+    <row r="121" spans="1:11" ht="32">
       <c r="A121" s="1" t="s">
         <v>0</v>
       </c>
@@ -6596,9 +6601,6 @@
         <v>74</v>
       </c>
     </row>
-    <row r="171" spans="1:5" ht="15.75"/>
-    <row r="173" spans="1:5" ht="15.75"/>
-    <row r="175" spans="1:5" ht="15.75"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -6607,10 +6609,10 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79081217-5F1E-2841-B0CC-D491E658A012}">
-  <dimension ref="A1:K835"/>
-  <sheetFormatPr defaultColWidth="10.625" defaultRowHeight="15.95"/>
+  <dimension ref="A1:K810"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.58203125" defaultRowHeight="16"/>
   <sheetData>
-    <row r="1" spans="1:7" ht="32.1">
+    <row r="1" spans="1:7" ht="32">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8248,12 +8250,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="74" spans="1:8" ht="20.100000000000001">
+    <row r="74" spans="1:8" ht="20">
       <c r="A74" s="13" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="75" spans="1:8" ht="16.5">
+    <row r="75" spans="1:8" ht="17">
       <c r="A75" s="14" t="s">
         <v>20</v>
       </c>
@@ -8277,7 +8279,7 @@
       </c>
       <c r="H75" s="14"/>
     </row>
-    <row r="76" spans="1:8" ht="16.5">
+    <row r="76" spans="1:8" ht="17">
       <c r="A76" s="14" t="s">
         <v>5</v>
       </c>
@@ -8301,13 +8303,12 @@
       </c>
       <c r="H76" s="14"/>
     </row>
-    <row r="77" spans="1:8" ht="15.75"/>
-    <row r="78" spans="1:8" ht="20.25">
+    <row r="78" spans="1:8" ht="20">
       <c r="A78" s="13" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="79" spans="1:8" ht="16.5">
+    <row r="79" spans="1:8" ht="17">
       <c r="A79" s="14" t="s">
         <v>20</v>
       </c>
@@ -8331,7 +8332,7 @@
       </c>
       <c r="H79" s="14"/>
     </row>
-    <row r="80" spans="1:8" ht="16.5">
+    <row r="80" spans="1:8" ht="17">
       <c r="A80" s="14" t="s">
         <v>6</v>
       </c>
@@ -8360,12 +8361,12 @@
         <v>28</v>
       </c>
     </row>
-    <row r="84" spans="1:7" ht="20.100000000000001">
+    <row r="84" spans="1:7" ht="20">
       <c r="A84" s="13" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="85" spans="1:7" ht="17.100000000000001">
+    <row r="85" spans="1:7" ht="17">
       <c r="A85" s="14" t="s">
         <v>30</v>
       </c>
@@ -8378,7 +8379,7 @@
       <c r="F85" s="14"/>
       <c r="G85" s="14"/>
     </row>
-    <row r="86" spans="1:7" ht="17.100000000000001">
+    <row r="86" spans="1:7" ht="17">
       <c r="A86" s="14">
         <v>5</v>
       </c>
@@ -8391,7 +8392,7 @@
       <c r="F86" s="14"/>
       <c r="G86" s="14"/>
     </row>
-    <row r="87" spans="1:7" ht="17.100000000000001">
+    <row r="87" spans="1:7" ht="17">
       <c r="A87" s="14">
         <v>61</v>
       </c>
@@ -8404,7 +8405,7 @@
       <c r="F87" s="14"/>
       <c r="G87" s="14"/>
     </row>
-    <row r="88" spans="1:7" ht="17.100000000000001">
+    <row r="88" spans="1:7" ht="17">
       <c r="A88" s="14">
         <v>67</v>
       </c>
@@ -8417,7 +8418,7 @@
       <c r="F88" s="14"/>
       <c r="G88" s="14"/>
     </row>
-    <row r="89" spans="1:7" ht="17.100000000000001">
+    <row r="89" spans="1:7" ht="17">
       <c r="A89" s="14">
         <v>68</v>
       </c>
@@ -8430,7 +8431,7 @@
       <c r="F89" s="14"/>
       <c r="G89" s="14"/>
     </row>
-    <row r="90" spans="1:7" ht="17.100000000000001">
+    <row r="90" spans="1:7" ht="17">
       <c r="A90" s="14">
         <v>69</v>
       </c>
@@ -8443,7 +8444,7 @@
       <c r="F90" s="14"/>
       <c r="G90" s="14"/>
     </row>
-    <row r="91" spans="1:7" ht="17.100000000000001">
+    <row r="91" spans="1:7" ht="17">
       <c r="A91" s="14">
         <v>70</v>
       </c>
@@ -8456,10 +8457,10 @@
       <c r="F91" s="14"/>
       <c r="G91" s="14"/>
     </row>
-    <row r="92" spans="1:7" ht="17.100000000000001">
+    <row r="92" spans="1:7" ht="17">
       <c r="A92" s="16"/>
     </row>
-    <row r="94" spans="1:7" ht="32.1">
+    <row r="94" spans="1:7" ht="32">
       <c r="A94" s="1" t="s">
         <v>0</v>
       </c>
@@ -10110,7 +10111,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="167" spans="1:8" ht="32.1">
+    <row r="167" spans="1:8" ht="32">
       <c r="A167" s="1" t="s">
         <v>0</v>
       </c>
@@ -11610,12 +11611,12 @@
         <v>28</v>
       </c>
     </row>
-    <row r="234" spans="1:7" ht="20.100000000000001">
+    <row r="234" spans="1:7" ht="20">
       <c r="A234" s="13" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="235" spans="1:7" ht="17.100000000000001">
+    <row r="235" spans="1:7" ht="17">
       <c r="A235" s="14" t="s">
         <v>30</v>
       </c>
@@ -11628,7 +11629,7 @@
       <c r="F235" s="14"/>
       <c r="G235" s="14"/>
     </row>
-    <row r="236" spans="1:7" ht="17.100000000000001">
+    <row r="236" spans="1:7" ht="17">
       <c r="A236" s="14">
         <v>26</v>
       </c>
@@ -11641,7 +11642,7 @@
       <c r="F236" s="14"/>
       <c r="G236" s="14"/>
     </row>
-    <row r="237" spans="1:7" ht="17.100000000000001">
+    <row r="237" spans="1:7" ht="17">
       <c r="A237" s="14">
         <v>58</v>
       </c>
@@ -11654,7 +11655,7 @@
       <c r="F237" s="14"/>
       <c r="G237" s="14"/>
     </row>
-    <row r="238" spans="1:7" ht="17.100000000000001">
+    <row r="238" spans="1:7" ht="17">
       <c r="A238" s="14">
         <v>60</v>
       </c>
@@ -11667,7 +11668,7 @@
       <c r="F238" s="14"/>
       <c r="G238" s="14"/>
     </row>
-    <row r="239" spans="1:7" ht="17.100000000000001">
+    <row r="239" spans="1:7" ht="17">
       <c r="A239" s="14">
         <v>61</v>
       </c>
@@ -11680,7 +11681,7 @@
       <c r="F239" s="14"/>
       <c r="G239" s="14"/>
     </row>
-    <row r="240" spans="1:7" ht="17.100000000000001">
+    <row r="240" spans="1:7" ht="17">
       <c r="A240" s="14">
         <v>62</v>
       </c>
@@ -11693,7 +11694,7 @@
       <c r="F240" s="14"/>
       <c r="G240" s="14"/>
     </row>
-    <row r="241" spans="1:7" ht="17.100000000000001">
+    <row r="241" spans="1:7" ht="17">
       <c r="A241" s="14">
         <v>63</v>
       </c>
@@ -11706,7 +11707,7 @@
       <c r="F241" s="14"/>
       <c r="G241" s="14"/>
     </row>
-    <row r="242" spans="1:7" ht="17.100000000000001">
+    <row r="242" spans="1:7" ht="17">
       <c r="A242" s="14">
         <v>64</v>
       </c>
@@ -11719,8 +11720,7 @@
       <c r="F242" s="14"/>
       <c r="G242" s="14"/>
     </row>
-    <row r="243" spans="1:7" ht="15.75"/>
-    <row r="245" spans="1:7" ht="32.1">
+    <row r="245" spans="1:7" ht="32">
       <c r="A245" s="1" t="s">
         <v>0</v>
       </c>
@@ -13236,7 +13236,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="312" spans="1:8" ht="32.1">
+    <row r="312" spans="1:8" ht="32">
       <c r="A312" s="1" t="s">
         <v>0</v>
       </c>
@@ -14575,12 +14575,12 @@
         <v>28</v>
       </c>
     </row>
-    <row r="372" spans="1:7" ht="20.100000000000001">
+    <row r="372" spans="1:7" ht="20">
       <c r="A372" s="13" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="373" spans="1:7" ht="17.100000000000001">
+    <row r="373" spans="1:7" ht="17">
       <c r="A373" s="14" t="s">
         <v>30</v>
       </c>
@@ -14593,7 +14593,7 @@
       <c r="F373" s="14"/>
       <c r="G373" s="14"/>
     </row>
-    <row r="374" spans="1:7" ht="17.100000000000001">
+    <row r="374" spans="1:7" ht="17">
       <c r="A374" s="14">
         <v>11</v>
       </c>
@@ -14606,7 +14606,7 @@
       <c r="F374" s="14"/>
       <c r="G374" s="14"/>
     </row>
-    <row r="375" spans="1:7" ht="17.100000000000001">
+    <row r="375" spans="1:7" ht="17">
       <c r="A375" s="14">
         <v>28</v>
       </c>
@@ -14619,7 +14619,7 @@
       <c r="F375" s="14"/>
       <c r="G375" s="14"/>
     </row>
-    <row r="376" spans="1:7" ht="17.100000000000001">
+    <row r="376" spans="1:7" ht="17">
       <c r="A376" s="14">
         <v>41</v>
       </c>
@@ -14632,7 +14632,7 @@
       <c r="F376" s="14"/>
       <c r="G376" s="14"/>
     </row>
-    <row r="377" spans="1:7" ht="17.100000000000001">
+    <row r="377" spans="1:7" ht="17">
       <c r="A377" s="14">
         <v>47</v>
       </c>
@@ -14645,7 +14645,7 @@
       <c r="F377" s="14"/>
       <c r="G377" s="14"/>
     </row>
-    <row r="378" spans="1:7" ht="17.100000000000001">
+    <row r="378" spans="1:7" ht="17">
       <c r="A378" s="14">
         <v>56</v>
       </c>
@@ -14658,7 +14658,7 @@
       <c r="F378" s="14"/>
       <c r="G378" s="14"/>
     </row>
-    <row r="379" spans="1:7" ht="17.100000000000001">
+    <row r="379" spans="1:7" ht="17">
       <c r="A379" s="14">
         <v>57</v>
       </c>
@@ -14671,7 +14671,7 @@
       <c r="F379" s="14"/>
       <c r="G379" s="14"/>
     </row>
-    <row r="381" spans="1:7" ht="32.1">
+    <row r="381" spans="1:7" ht="32">
       <c r="A381" s="1" t="s">
         <v>0</v>
       </c>
@@ -16023,7 +16023,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="441" spans="1:8" ht="32.1">
+    <row r="441" spans="1:8" ht="32">
       <c r="A441" s="1" t="s">
         <v>0</v>
       </c>
@@ -17224,12 +17224,12 @@
         <v>28</v>
       </c>
     </row>
-    <row r="495" spans="1:7" ht="20.100000000000001">
+    <row r="495" spans="1:7" ht="20">
       <c r="A495" s="13" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="496" spans="1:7" ht="17.100000000000001">
+    <row r="496" spans="1:7" ht="17">
       <c r="A496" s="14" t="s">
         <v>30</v>
       </c>
@@ -17242,7 +17242,7 @@
       <c r="F496" s="14"/>
       <c r="G496" s="14"/>
     </row>
-    <row r="497" spans="1:7" ht="17.100000000000001">
+    <row r="497" spans="1:7" ht="17">
       <c r="A497" s="14">
         <v>20</v>
       </c>
@@ -17255,7 +17255,7 @@
       <c r="F497" s="14"/>
       <c r="G497" s="14"/>
     </row>
-    <row r="498" spans="1:7" ht="17.100000000000001">
+    <row r="498" spans="1:7" ht="17">
       <c r="A498" s="14">
         <v>36</v>
       </c>
@@ -17268,7 +17268,7 @@
       <c r="F498" s="14"/>
       <c r="G498" s="14"/>
     </row>
-    <row r="499" spans="1:7" ht="17.100000000000001">
+    <row r="499" spans="1:7" ht="17">
       <c r="A499" s="14">
         <v>44</v>
       </c>
@@ -17281,7 +17281,7 @@
       <c r="F499" s="14"/>
       <c r="G499" s="14"/>
     </row>
-    <row r="500" spans="1:7" ht="17.100000000000001">
+    <row r="500" spans="1:7" ht="17">
       <c r="A500" s="14">
         <v>50</v>
       </c>
@@ -17294,7 +17294,7 @@
       <c r="F500" s="14"/>
       <c r="G500" s="14"/>
     </row>
-    <row r="501" spans="1:7" ht="17.100000000000001">
+    <row r="501" spans="1:7" ht="17">
       <c r="A501" s="14">
         <v>51</v>
       </c>
@@ -17307,7 +17307,7 @@
       <c r="F501" s="14"/>
       <c r="G501" s="14"/>
     </row>
-    <row r="503" spans="1:7" ht="32.1">
+    <row r="503" spans="1:7" ht="32">
       <c r="A503" s="1" t="s">
         <v>0</v>
       </c>
@@ -18518,7 +18518,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="557" spans="1:8" ht="32.1">
+    <row r="557" spans="1:8" ht="32">
       <c r="A557" s="1" t="s">
         <v>0</v>
       </c>
@@ -19599,17 +19599,17 @@
         <v>1993.4419999999996</v>
       </c>
     </row>
-    <row r="605" spans="1:7" ht="15.75">
+    <row r="605" spans="1:7">
       <c r="A605" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="606" spans="1:7" ht="20.100000000000001">
+    <row r="606" spans="1:7" ht="20">
       <c r="A606" s="13" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="607" spans="1:7" ht="17.100000000000001">
+    <row r="607" spans="1:7" ht="17">
       <c r="A607" s="14" t="s">
         <v>30</v>
       </c>
@@ -19621,7 +19621,7 @@
       <c r="E607" s="14"/>
       <c r="F607" s="14"/>
     </row>
-    <row r="608" spans="1:7" ht="17.100000000000001">
+    <row r="608" spans="1:7" ht="17">
       <c r="A608" s="14">
         <v>28</v>
       </c>
@@ -19633,7 +19633,7 @@
       <c r="E608" s="14"/>
       <c r="F608" s="14"/>
     </row>
-    <row r="609" spans="1:7" ht="17.100000000000001">
+    <row r="609" spans="1:7" ht="17">
       <c r="A609" s="14">
         <v>38</v>
       </c>
@@ -19645,7 +19645,7 @@
       <c r="E609" s="14"/>
       <c r="F609" s="14"/>
     </row>
-    <row r="610" spans="1:7" ht="17.100000000000001">
+    <row r="610" spans="1:7" ht="17">
       <c r="A610" s="14">
         <v>39</v>
       </c>
@@ -19657,7 +19657,7 @@
       <c r="E610" s="14"/>
       <c r="F610" s="14"/>
     </row>
-    <row r="611" spans="1:7" ht="17.100000000000001">
+    <row r="611" spans="1:7" ht="17">
       <c r="A611" s="14">
         <v>46</v>
       </c>
@@ -19669,10 +19669,10 @@
       <c r="E611" s="14"/>
       <c r="F611" s="14"/>
     </row>
-    <row r="612" spans="1:7" ht="17.100000000000001">
+    <row r="612" spans="1:7" ht="17">
       <c r="A612" s="16"/>
     </row>
-    <row r="614" spans="1:7" ht="32.1">
+    <row r="614" spans="1:7" ht="32">
       <c r="A614" s="1" t="s">
         <v>0</v>
       </c>
@@ -20765,7 +20765,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="663" spans="1:8" ht="32.1">
+    <row r="663" spans="1:8" ht="32">
       <c r="A663" s="1" t="s">
         <v>0</v>
       </c>
@@ -21759,7 +21759,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="709" spans="1:7" ht="20.100000000000001">
+    <row r="709" spans="1:7" ht="20">
       <c r="A709" s="10" t="s">
         <v>33</v>
       </c>
@@ -21767,7 +21767,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="710" spans="1:7" ht="20.100000000000001">
+    <row r="710" spans="1:7" ht="20">
       <c r="A710" s="33">
         <v>42</v>
       </c>
@@ -21775,7 +21775,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="711" spans="1:7" ht="20.100000000000001">
+    <row r="711" spans="1:7" ht="20">
       <c r="A711" s="10" t="s">
         <v>76</v>
       </c>
@@ -21783,7 +21783,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="712" spans="1:7" ht="20.100000000000001">
+    <row r="712" spans="1:7" ht="20">
       <c r="A712" s="10">
         <v>1</v>
       </c>
@@ -21791,7 +21791,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="713" spans="1:7" ht="20.100000000000001">
+    <row r="713" spans="1:7" ht="20">
       <c r="A713" s="10" t="s">
         <v>34</v>
       </c>
@@ -21799,7 +21799,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="714" spans="1:7" ht="20.100000000000001">
+    <row r="714" spans="1:7" ht="20">
       <c r="A714" s="10" t="s">
         <v>0</v>
       </c>
@@ -21812,37 +21812,27 @@
         <v>81</v>
       </c>
     </row>
-    <row r="718" spans="1:7" ht="15.75"/>
-    <row r="719" spans="1:7" ht="15.75"/>
-    <row r="720" spans="1:7" ht="15.75"/>
-    <row r="721" spans="1:1" ht="15.75"/>
-    <row r="722" spans="1:1" ht="15.75"/>
-    <row r="725" spans="1:1" ht="15.75"/>
-    <row r="726" spans="1:1" ht="15.75"/>
-    <row r="727" spans="1:1" ht="15.75"/>
-    <row r="730" spans="1:1" ht="15.75"/>
-    <row r="731" spans="1:1" ht="15.75"/>
-    <row r="732" spans="1:1" ht="20.25">
+    <row r="732" spans="1:1" ht="20">
       <c r="A732" s="13" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="733" spans="1:1" ht="16.5">
+    <row r="733" spans="1:1" ht="17">
       <c r="A733" s="14" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="734" spans="1:1" ht="16.5">
+    <row r="734" spans="1:1" ht="17">
       <c r="A734" s="15">
         <v>0</v>
       </c>
     </row>
-    <row r="736" spans="1:1" ht="20.25">
+    <row r="736" spans="1:1" ht="20">
       <c r="A736" s="13" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="737" spans="1:11" ht="16.5">
+    <row r="737" spans="1:11" ht="17">
       <c r="A737" s="14" t="s">
         <v>87</v>
       </c>
@@ -21852,7 +21842,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="740" spans="1:11" ht="32.1">
+    <row r="740" spans="1:11" ht="32">
       <c r="A740" s="1" t="s">
         <v>0</v>
       </c>
@@ -23655,8 +23645,6 @@
         <v>74</v>
       </c>
     </row>
-    <row r="823" ht="15.75"/>
-    <row r="835" ht="15.75"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -23666,11 +23654,11 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B7C509C-A6FE-014C-95B9-A191384F244B}">
   <dimension ref="A1:F23"/>
-  <sheetFormatPr defaultColWidth="10.625" defaultRowHeight="15.95"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.58203125" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
     <col min="2" max="2" width="15.5" customWidth="1"/>
-    <col min="5" max="6" width="21.125" customWidth="1"/>
+    <col min="5" max="6" width="21.08203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -23904,14 +23892,14 @@
   <sheetPr>
     <tabColor theme="0"/>
   </sheetPr>
-  <dimension ref="A1:K469"/>
-  <sheetFormatPr defaultColWidth="10.625" defaultRowHeight="15.95"/>
+  <dimension ref="A1:K455"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.58203125" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
-    <col min="2" max="2" width="20.625" customWidth="1"/>
+    <col min="2" max="2" width="20.58203125" customWidth="1"/>
     <col min="3" max="3" width="13.25" customWidth="1"/>
     <col min="4" max="4" width="18.5" customWidth="1"/>
-    <col min="5" max="5" width="16.625" customWidth="1"/>
+    <col min="5" max="5" width="16.58203125" customWidth="1"/>
     <col min="6" max="6" width="18" customWidth="1"/>
     <col min="7" max="7" width="16" customWidth="1"/>
     <col min="8" max="8" width="15.5" customWidth="1"/>
@@ -24798,12 +24786,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="41" spans="1:9" ht="20.100000000000001">
+    <row r="41" spans="1:9" ht="20">
       <c r="A41" s="13" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="42" spans="1:9" ht="16.5">
+    <row r="42" spans="1:9" ht="17">
       <c r="A42" s="14" t="s">
         <v>20</v>
       </c>
@@ -24827,7 +24815,7 @@
       </c>
       <c r="I42" s="14"/>
     </row>
-    <row r="43" spans="1:9" ht="16.5">
+    <row r="43" spans="1:9" ht="17">
       <c r="A43" s="14" t="s">
         <v>5</v>
       </c>
@@ -24851,13 +24839,12 @@
       </c>
       <c r="I43" s="14"/>
     </row>
-    <row r="44" spans="1:9" ht="15.75"/>
-    <row r="45" spans="1:9" ht="20.25">
+    <row r="45" spans="1:9" ht="20">
       <c r="A45" s="13" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="46" spans="1:9" ht="16.5">
+    <row r="46" spans="1:9" ht="17">
       <c r="A46" s="14" t="s">
         <v>20</v>
       </c>
@@ -24881,7 +24868,7 @@
       </c>
       <c r="I46" s="14"/>
     </row>
-    <row r="47" spans="1:9" ht="16.5">
+    <row r="47" spans="1:9" ht="17">
       <c r="A47" s="14" t="s">
         <v>27</v>
       </c>
@@ -24910,12 +24897,12 @@
         <v>28</v>
       </c>
     </row>
-    <row r="51" spans="1:7" ht="20.100000000000001">
+    <row r="51" spans="1:7" ht="20">
       <c r="A51" s="13" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="52" spans="1:7" ht="17.100000000000001">
+    <row r="52" spans="1:7" ht="17">
       <c r="A52" s="14" t="s">
         <v>30</v>
       </c>
@@ -24928,7 +24915,7 @@
       <c r="F52" s="14"/>
       <c r="G52" s="14"/>
     </row>
-    <row r="53" spans="1:7" ht="17.100000000000001">
+    <row r="53" spans="1:7" ht="17">
       <c r="A53" s="14">
         <v>17</v>
       </c>
@@ -24941,7 +24928,7 @@
       <c r="F53" s="14"/>
       <c r="G53" s="14"/>
     </row>
-    <row r="54" spans="1:7" ht="17.100000000000001">
+    <row r="54" spans="1:7" ht="17">
       <c r="A54" s="14">
         <v>23</v>
       </c>
@@ -24954,7 +24941,7 @@
       <c r="F54" s="14"/>
       <c r="G54" s="14"/>
     </row>
-    <row r="55" spans="1:7" ht="17.100000000000001">
+    <row r="55" spans="1:7" ht="17">
       <c r="A55" s="14">
         <v>32</v>
       </c>
@@ -24967,7 +24954,7 @@
       <c r="F55" s="14"/>
       <c r="G55" s="14"/>
     </row>
-    <row r="56" spans="1:7" ht="17.100000000000001">
+    <row r="56" spans="1:7" ht="17">
       <c r="A56" s="14">
         <v>35</v>
       </c>
@@ -24980,7 +24967,7 @@
       <c r="F56" s="14"/>
       <c r="G56" s="14"/>
     </row>
-    <row r="57" spans="1:7" ht="17.100000000000001">
+    <row r="57" spans="1:7" ht="17">
       <c r="A57" s="14">
         <v>37</v>
       </c>
@@ -26646,12 +26633,12 @@
         <v>28</v>
       </c>
     </row>
-    <row r="133" spans="1:7" ht="20.100000000000001">
+    <row r="133" spans="1:7" ht="20">
       <c r="A133" s="13" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="134" spans="1:7" ht="17.100000000000001">
+    <row r="134" spans="1:7" ht="17">
       <c r="A134" s="14" t="s">
         <v>30</v>
       </c>
@@ -26664,7 +26651,7 @@
       <c r="F134" s="14"/>
       <c r="G134" s="14"/>
     </row>
-    <row r="135" spans="1:7" ht="17.100000000000001">
+    <row r="135" spans="1:7" ht="17">
       <c r="A135" s="14">
         <v>30</v>
       </c>
@@ -26677,7 +26664,7 @@
       <c r="F135" s="14"/>
       <c r="G135" s="14"/>
     </row>
-    <row r="136" spans="1:7" ht="17.100000000000001">
+    <row r="136" spans="1:7" ht="17">
       <c r="A136" s="14">
         <v>32</v>
       </c>
@@ -26690,7 +26677,6 @@
       <c r="F136" s="14"/>
       <c r="G136" s="14"/>
     </row>
-    <row r="137" spans="1:7" ht="15.75"/>
     <row r="138" spans="1:7">
       <c r="A138" s="1" t="s">
         <v>0</v>
@@ -27407,7 +27393,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="169" spans="1:11" ht="17.100000000000001">
+    <row r="169" spans="1:11" ht="17">
       <c r="A169" s="22">
         <v>73</v>
       </c>
@@ -27434,7 +27420,7 @@
       <c r="J169" s="14"/>
       <c r="K169" s="14"/>
     </row>
-    <row r="170" spans="1:11" ht="17.100000000000001">
+    <row r="170" spans="1:11" ht="17">
       <c r="A170" s="22">
         <v>80</v>
       </c>
@@ -27463,13 +27449,13 @@
       <c r="J170" s="14"/>
       <c r="K170" s="14"/>
     </row>
-    <row r="171" spans="1:11" ht="17.100000000000001">
+    <row r="171" spans="1:11" ht="17">
       <c r="H171" s="14"/>
       <c r="I171" s="14"/>
       <c r="J171" s="14"/>
       <c r="K171" s="14"/>
     </row>
-    <row r="172" spans="1:11" ht="17.100000000000001">
+    <row r="172" spans="1:11" ht="17">
       <c r="A172" s="1" t="s">
         <v>0</v>
       </c>
@@ -27910,7 +27896,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="191" spans="1:11" ht="17.100000000000001">
+    <row r="191" spans="1:11" ht="17">
       <c r="A191" s="22">
         <v>43</v>
       </c>
@@ -27934,7 +27920,7 @@
       </c>
       <c r="K191" s="14"/>
     </row>
-    <row r="192" spans="1:11" ht="17.100000000000001">
+    <row r="192" spans="1:11" ht="17">
       <c r="A192" s="22">
         <v>45</v>
       </c>
@@ -28192,18 +28178,18 @@
       <c r="A203" s="19"/>
       <c r="B203" s="19"/>
     </row>
-    <row r="204" spans="1:7" ht="30.75">
+    <row r="204" spans="1:7" ht="32">
       <c r="A204" s="19" t="s">
         <v>28</v>
       </c>
       <c r="B204" s="19"/>
     </row>
-    <row r="205" spans="1:7" ht="20.100000000000001">
+    <row r="205" spans="1:7" ht="20">
       <c r="A205" s="13" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="206" spans="1:7" ht="17.100000000000001">
+    <row r="206" spans="1:7" ht="17">
       <c r="A206" s="14" t="s">
         <v>30</v>
       </c>
@@ -28216,7 +28202,7 @@
       <c r="F206" s="14"/>
       <c r="G206" s="14"/>
     </row>
-    <row r="207" spans="1:7" ht="17.100000000000001">
+    <row r="207" spans="1:7" ht="17">
       <c r="A207" s="14">
         <v>30</v>
       </c>
@@ -28229,14 +28215,14 @@
       <c r="F207" s="14"/>
       <c r="G207" s="14"/>
     </row>
-    <row r="208" spans="1:7" ht="17.100000000000001">
+    <row r="208" spans="1:7" ht="17">
       <c r="A208" s="16"/>
     </row>
     <row r="209" spans="1:11">
       <c r="A209" s="19"/>
       <c r="B209" s="19"/>
     </row>
-    <row r="210" spans="1:11" ht="17.100000000000001">
+    <row r="210" spans="1:11" ht="17">
       <c r="A210" s="1" t="s">
         <v>0</v>
       </c>
@@ -28677,7 +28663,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="229" spans="1:11" ht="17.100000000000001">
+    <row r="229" spans="1:11" ht="17">
       <c r="A229" s="22">
         <v>43</v>
       </c>
@@ -28701,7 +28687,7 @@
       </c>
       <c r="K229" s="14"/>
     </row>
-    <row r="230" spans="1:11" ht="17.100000000000001">
+    <row r="230" spans="1:11" ht="17">
       <c r="A230" s="22">
         <v>45</v>
       </c>
@@ -29656,18 +29642,18 @@
       <c r="A272" s="19"/>
       <c r="B272" s="19"/>
     </row>
-    <row r="273" spans="1:7" ht="30.75">
+    <row r="273" spans="1:7" ht="32">
       <c r="A273" s="19" t="s">
         <v>28</v>
       </c>
       <c r="B273" s="19"/>
     </row>
-    <row r="274" spans="1:7" ht="20.100000000000001">
+    <row r="274" spans="1:7" ht="20">
       <c r="A274" s="13" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="275" spans="1:7" ht="17.100000000000001">
+    <row r="275" spans="1:7" ht="17">
       <c r="A275" s="14" t="s">
         <v>30</v>
       </c>
@@ -29679,7 +29665,7 @@
       <c r="E275" s="14"/>
       <c r="F275" s="14"/>
     </row>
-    <row r="276" spans="1:7" ht="17.100000000000001">
+    <row r="276" spans="1:7" ht="17">
       <c r="A276" s="14">
         <v>18</v>
       </c>
@@ -29691,7 +29677,7 @@
       <c r="E276" s="14"/>
       <c r="F276" s="14"/>
     </row>
-    <row r="277" spans="1:7" ht="17.100000000000001">
+    <row r="277" spans="1:7" ht="17">
       <c r="A277" s="16"/>
     </row>
     <row r="278" spans="1:7">
@@ -31070,7 +31056,7 @@
       <c r="A340" s="19"/>
       <c r="B340" s="19"/>
     </row>
-    <row r="341" spans="1:7" ht="30.75">
+    <row r="341" spans="1:7" ht="32">
       <c r="A341" s="19" t="s">
         <v>28</v>
       </c>
@@ -31084,7 +31070,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="343" spans="1:7" ht="20.100000000000001">
+    <row r="343" spans="1:7" ht="20">
       <c r="A343" s="10" t="s">
         <v>33</v>
       </c>
@@ -31093,7 +31079,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="344" spans="1:7" ht="20.100000000000001">
+    <row r="344" spans="1:7" ht="20">
       <c r="A344" s="33">
         <v>28</v>
       </c>
@@ -31102,7 +31088,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="345" spans="1:7" ht="20.100000000000001">
+    <row r="345" spans="1:7" ht="20">
       <c r="A345" s="10" t="s">
         <v>34</v>
       </c>
@@ -31111,7 +31097,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="346" spans="1:7" ht="20.100000000000001">
+    <row r="346" spans="1:7" ht="20">
       <c r="A346" s="10" t="s">
         <v>0</v>
       </c>
@@ -31809,84 +31795,84 @@
       <c r="A380" s="19"/>
       <c r="B380" s="19"/>
     </row>
-    <row r="381" spans="1:10" ht="15.75">
+    <row r="381" spans="1:10">
       <c r="A381" s="19"/>
       <c r="B381" s="19"/>
     </row>
-    <row r="382" spans="1:10" ht="16.5">
+    <row r="382" spans="1:10" ht="17">
       <c r="A382" s="19"/>
       <c r="B382" s="19"/>
       <c r="H382" s="14"/>
       <c r="I382" s="14"/>
       <c r="J382" s="14"/>
     </row>
-    <row r="383" spans="1:10" ht="16.5">
+    <row r="383" spans="1:10" ht="17">
       <c r="A383" s="19"/>
       <c r="B383" s="19"/>
       <c r="H383" s="14"/>
       <c r="I383" s="14"/>
       <c r="J383" s="14"/>
     </row>
-    <row r="384" spans="1:10" ht="16.5">
+    <row r="384" spans="1:10" ht="17">
       <c r="A384" s="19"/>
       <c r="B384" s="19"/>
       <c r="H384" s="14"/>
       <c r="I384" s="14"/>
       <c r="J384" s="14"/>
     </row>
-    <row r="385" spans="1:11" ht="16.5">
+    <row r="385" spans="1:11" ht="17">
       <c r="A385" s="19"/>
       <c r="B385" s="19"/>
       <c r="H385" s="14"/>
       <c r="I385" s="14"/>
       <c r="J385" s="14"/>
     </row>
-    <row r="386" spans="1:11" ht="15.75">
+    <row r="386" spans="1:11">
       <c r="A386" s="19"/>
       <c r="B386" s="19"/>
     </row>
-    <row r="387" spans="1:11" ht="15.75">
+    <row r="387" spans="1:11">
       <c r="A387" s="19"/>
       <c r="B387" s="19"/>
     </row>
-    <row r="388" spans="1:11" ht="16.5">
+    <row r="388" spans="1:11" ht="17">
       <c r="A388" s="19"/>
       <c r="B388" s="19"/>
       <c r="F388" s="14"/>
     </row>
-    <row r="389" spans="1:11" ht="16.5">
+    <row r="389" spans="1:11" ht="17">
       <c r="A389" s="19"/>
       <c r="B389" s="19"/>
       <c r="F389" s="15"/>
     </row>
-    <row r="390" spans="1:11" ht="15.75">
+    <row r="390" spans="1:11">
       <c r="A390" s="19"/>
       <c r="B390" s="19"/>
     </row>
-    <row r="391" spans="1:11" ht="20.25">
+    <row r="391" spans="1:11" ht="20">
       <c r="A391" s="13" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="392" spans="1:11" ht="16.5">
+    <row r="392" spans="1:11" ht="17">
       <c r="A392" s="14" t="s">
         <v>37</v>
       </c>
       <c r="B392" s="14"/>
       <c r="C392" s="14"/>
     </row>
-    <row r="393" spans="1:11" ht="16.5">
+    <row r="393" spans="1:11" ht="17">
       <c r="A393" s="15">
         <v>0.80310000000000004</v>
       </c>
       <c r="B393" s="14"/>
       <c r="C393" s="14"/>
     </row>
-    <row r="394" spans="1:11" ht="16.5">
+    <row r="394" spans="1:11" ht="17">
       <c r="B394" s="14"/>
       <c r="C394" s="14"/>
     </row>
-    <row r="395" spans="1:11" ht="20.25">
+    <row r="395" spans="1:11" ht="20">
       <c r="A395" s="13" t="s">
         <v>38</v>
       </c>
@@ -31897,7 +31883,7 @@
       <c r="H395" s="14"/>
       <c r="I395" s="14"/>
     </row>
-    <row r="396" spans="1:11" ht="16.5">
+    <row r="396" spans="1:11" ht="17">
       <c r="A396" s="14" t="s">
         <v>39</v>
       </c>
@@ -31912,7 +31898,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="399" spans="1:11" ht="26.1">
+    <row r="399" spans="1:11" ht="26">
       <c r="A399" s="1" t="s">
         <v>0</v>
       </c>
@@ -33211,10 +33197,6 @@
         <v>74</v>
       </c>
     </row>
-    <row r="456" spans="1:5" ht="15.75"/>
-    <row r="459" spans="1:5" ht="15.75"/>
-    <row r="460" spans="1:5" ht="15.75"/>
-    <row r="469" ht="15.75"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -33223,10 +33205,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D1CBC43-6DA5-9C4C-89FA-F1020C8FBB03}">
-  <dimension ref="A1:K163"/>
-  <sheetFormatPr defaultColWidth="10.625" defaultRowHeight="15.95"/>
+  <dimension ref="A1:K160"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.58203125" defaultRowHeight="16"/>
   <sheetData>
-    <row r="1" spans="1:7" ht="32.1">
+    <row r="1" spans="1:7" ht="32">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -33530,12 +33512,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="20.100000000000001">
+    <row r="16" spans="1:7" ht="20">
       <c r="A16" s="13" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="16.5">
+    <row r="17" spans="1:10" ht="17">
       <c r="A17" s="14" t="s">
         <v>20</v>
       </c>
@@ -33560,7 +33542,7 @@
       <c r="H17" s="14"/>
       <c r="J17" s="14"/>
     </row>
-    <row r="18" spans="1:10" ht="16.5">
+    <row r="18" spans="1:10" ht="17">
       <c r="A18" s="14" t="s">
         <v>5</v>
       </c>
@@ -33585,13 +33567,12 @@
       <c r="H18" s="14"/>
       <c r="J18" s="14"/>
     </row>
-    <row r="19" spans="1:10" ht="15.75"/>
-    <row r="20" spans="1:10" ht="20.25">
+    <row r="20" spans="1:10" ht="20">
       <c r="A20" s="13" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="16.5">
+    <row r="21" spans="1:10" ht="17">
       <c r="A21" s="14" t="s">
         <v>20</v>
       </c>
@@ -33616,7 +33597,7 @@
       <c r="H21" s="14"/>
       <c r="J21" s="14"/>
     </row>
-    <row r="22" spans="1:10" ht="16.5">
+    <row r="22" spans="1:10" ht="17">
       <c r="A22" s="14" t="s">
         <v>6</v>
       </c>
@@ -33646,12 +33627,12 @@
         <v>28</v>
       </c>
     </row>
-    <row r="26" spans="1:10" ht="20.100000000000001">
+    <row r="26" spans="1:10" ht="20">
       <c r="A26" s="13" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="27" spans="1:10" ht="17.100000000000001">
+    <row r="27" spans="1:10" ht="17">
       <c r="A27" s="14" t="s">
         <v>30</v>
       </c>
@@ -33663,7 +33644,7 @@
       <c r="E27" s="14"/>
       <c r="F27" s="14"/>
     </row>
-    <row r="28" spans="1:10" ht="17.100000000000001">
+    <row r="28" spans="1:10" ht="17">
       <c r="A28" s="14">
         <v>1</v>
       </c>
@@ -33675,7 +33656,7 @@
       <c r="E28" s="14"/>
       <c r="F28" s="14"/>
     </row>
-    <row r="29" spans="1:10" ht="17.100000000000001">
+    <row r="29" spans="1:10" ht="17">
       <c r="A29" s="14">
         <v>3</v>
       </c>
@@ -33687,10 +33668,10 @@
       <c r="E29" s="14"/>
       <c r="F29" s="14"/>
     </row>
-    <row r="30" spans="1:10" ht="17.100000000000001">
+    <row r="30" spans="1:10" ht="17">
       <c r="A30" s="16"/>
     </row>
-    <row r="32" spans="1:10" ht="32.1">
+    <row r="32" spans="1:10" ht="32">
       <c r="A32" s="1" t="s">
         <v>0</v>
       </c>
@@ -33995,7 +33976,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="47" spans="1:8" ht="32.1">
+    <row r="47" spans="1:8" ht="32">
       <c r="A47" s="1" t="s">
         <v>0</v>
       </c>
@@ -34261,7 +34242,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="88" spans="1:4" ht="20.100000000000001">
+    <row r="88" spans="1:4" ht="20">
       <c r="A88" s="10" t="s">
         <v>33</v>
       </c>
@@ -34269,7 +34250,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="89" spans="1:4" ht="20.100000000000001">
+    <row r="89" spans="1:4" ht="20">
       <c r="A89" s="33">
         <v>10</v>
       </c>
@@ -34277,7 +34258,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="90" spans="1:4" ht="20.100000000000001">
+    <row r="90" spans="1:4" ht="20">
       <c r="A90" s="10" t="s">
         <v>76</v>
       </c>
@@ -34285,7 +34266,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="91" spans="1:4" ht="20.100000000000001">
+    <row r="91" spans="1:4" ht="20">
       <c r="A91" s="10">
         <v>1</v>
       </c>
@@ -34293,7 +34274,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:4" ht="20.100000000000001">
+    <row r="92" spans="1:4" ht="20">
       <c r="A92" s="10" t="s">
         <v>34</v>
       </c>
@@ -34301,7 +34282,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="93" spans="1:4" ht="20.100000000000001">
+    <row r="93" spans="1:4" ht="20">
       <c r="A93" s="10" t="s">
         <v>0</v>
       </c>
@@ -34309,71 +34290,55 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:4" ht="20.100000000000001">
+    <row r="94" spans="1:4" ht="20">
       <c r="A94" s="10"/>
       <c r="D94" s="10"/>
     </row>
-    <row r="95" spans="1:4" ht="20.100000000000001">
+    <row r="95" spans="1:4" ht="20">
       <c r="A95" s="10"/>
       <c r="D95" s="10"/>
     </row>
-    <row r="96" spans="1:4" ht="20.25">
+    <row r="96" spans="1:4" ht="20">
       <c r="A96" s="19" t="s">
         <v>35</v>
       </c>
       <c r="D96" s="10"/>
     </row>
-    <row r="97" spans="1:4" ht="20.100000000000001">
+    <row r="97" spans="1:4" ht="20">
       <c r="A97" s="10"/>
       <c r="D97" s="10"/>
     </row>
-    <row r="98" spans="1:4" ht="15.75"/>
-    <row r="99" spans="1:4" ht="15.75"/>
-    <row r="100" spans="1:4" ht="15.75"/>
-    <row r="101" spans="1:4" ht="15.75"/>
-    <row r="102" spans="1:4" ht="15.75"/>
-    <row r="103" spans="1:4" ht="15.75"/>
-    <row r="104" spans="1:4" ht="15.75"/>
-    <row r="105" spans="1:4" ht="15.75"/>
-    <row r="106" spans="1:4" ht="15.75"/>
-    <row r="107" spans="1:4" ht="15.75"/>
-    <row r="108" spans="1:4" ht="15.75"/>
-    <row r="109" spans="1:4" ht="15.75"/>
-    <row r="110" spans="1:4" ht="15.75"/>
-    <row r="111" spans="1:4" ht="15.75"/>
-    <row r="112" spans="1:4" ht="20.25">
+    <row r="112" spans="1:4" ht="20">
       <c r="A112" s="13" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="113" spans="1:11" ht="16.5">
+    <row r="113" spans="1:11" ht="17">
       <c r="A113" s="14" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="114" spans="1:11" ht="16.5">
+    <row r="114" spans="1:11" ht="17">
       <c r="A114" s="15">
         <v>0.54390000000000005</v>
       </c>
     </row>
-    <row r="115" spans="1:11" ht="15.75"/>
-    <row r="116" spans="1:11" ht="20.25">
+    <row r="116" spans="1:11" ht="20">
       <c r="A116" s="13" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="117" spans="1:11" ht="16.5">
+    <row r="117" spans="1:11" ht="17">
       <c r="A117" s="14" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="119" spans="1:11" ht="15.75"/>
     <row r="121" spans="1:11">
       <c r="A121" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="122" spans="1:11" ht="32.1">
+    <row r="122" spans="1:11" ht="32">
       <c r="A122" s="1" t="s">
         <v>0</v>
       </c>
@@ -35001,7 +34966,6 @@
         <v>74</v>
       </c>
     </row>
-    <row r="163" ht="15.75"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -35010,10 +34974,10 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E941198-00B1-4A40-8111-DC3B3EEC383A}">
-  <dimension ref="A1:M178"/>
-  <sheetFormatPr defaultColWidth="10.625" defaultRowHeight="15.95"/>
+  <dimension ref="A1:M140"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.58203125" defaultRowHeight="16"/>
   <sheetData>
-    <row r="1" spans="1:7" ht="32.1">
+    <row r="1" spans="1:7" ht="32">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -35363,12 +35327,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="20.100000000000001">
+    <row r="18" spans="1:7" ht="20">
       <c r="A18" s="13" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.5">
+    <row r="19" spans="1:7" ht="17">
       <c r="A19" s="14" t="s">
         <v>20</v>
       </c>
@@ -35391,7 +35355,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.5">
+    <row r="20" spans="1:7" ht="17">
       <c r="A20" s="14" t="s">
         <v>5</v>
       </c>
@@ -35414,13 +35378,12 @@
         <v>178</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="15.75"/>
-    <row r="22" spans="1:7" ht="20.25">
+    <row r="22" spans="1:7" ht="20">
       <c r="A22" s="13" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.5">
+    <row r="23" spans="1:7" ht="17">
       <c r="A23" s="14" t="s">
         <v>20</v>
       </c>
@@ -35443,7 +35406,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.5">
+    <row r="24" spans="1:7" ht="17">
       <c r="A24" s="14" t="s">
         <v>6</v>
       </c>
@@ -35471,12 +35434,12 @@
         <v>28</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="20.100000000000001">
+    <row r="28" spans="1:7" ht="20">
       <c r="A28" s="13" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="17.100000000000001">
+    <row r="29" spans="1:7" ht="17">
       <c r="A29" s="14" t="s">
         <v>30</v>
       </c>
@@ -35488,7 +35451,7 @@
       <c r="E29" s="14"/>
       <c r="F29" s="14"/>
     </row>
-    <row r="30" spans="1:7" ht="17.100000000000001">
+    <row r="30" spans="1:7" ht="17">
       <c r="A30" s="14">
         <v>1</v>
       </c>
@@ -35500,10 +35463,10 @@
       <c r="E30" s="14"/>
       <c r="F30" s="14"/>
     </row>
-    <row r="31" spans="1:7" ht="17.100000000000001">
+    <row r="31" spans="1:7" ht="17">
       <c r="A31" s="16"/>
     </row>
-    <row r="32" spans="1:7" ht="32.1">
+    <row r="32" spans="1:7" ht="32">
       <c r="A32" s="1" t="s">
         <v>0</v>
       </c>
@@ -35851,7 +35814,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="49" spans="1:7" ht="32.1">
+    <row r="49" spans="1:7" ht="32">
       <c r="A49" s="1" t="s">
         <v>0</v>
       </c>
@@ -36186,7 +36149,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="68" spans="1:4" ht="20.100000000000001">
+    <row r="68" spans="1:4" ht="20">
       <c r="A68" s="10" t="s">
         <v>33</v>
       </c>
@@ -36194,7 +36157,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="69" spans="1:4" ht="20.100000000000001">
+    <row r="69" spans="1:4" ht="20">
       <c r="A69" s="33">
         <v>13</v>
       </c>
@@ -36202,7 +36165,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="70" spans="1:4" ht="20.100000000000001">
+    <row r="70" spans="1:4" ht="20">
       <c r="A70" s="10" t="s">
         <v>76</v>
       </c>
@@ -36210,7 +36173,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="71" spans="1:4" ht="20.100000000000001">
+    <row r="71" spans="1:4" ht="20">
       <c r="A71" s="10">
         <v>1</v>
       </c>
@@ -36218,7 +36181,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:4" ht="20.100000000000001">
+    <row r="72" spans="1:4" ht="20">
       <c r="A72" s="10" t="s">
         <v>34</v>
       </c>
@@ -36226,7 +36189,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="73" spans="1:4" ht="20.100000000000001">
+    <row r="73" spans="1:4" ht="20">
       <c r="A73" s="10" t="s">
         <v>0</v>
       </c>
@@ -36234,7 +36197,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:4" ht="20.100000000000001">
+    <row r="74" spans="1:4" ht="20">
       <c r="A74" s="10"/>
       <c r="D74" s="10"/>
     </row>
@@ -36243,40 +36206,33 @@
         <v>35</v>
       </c>
     </row>
-    <row r="78" spans="1:4" ht="15.75"/>
-    <row r="79" spans="1:4" ht="15.75"/>
-    <row r="80" spans="1:4" ht="15.75"/>
-    <row r="81" spans="1:13" ht="15.75"/>
-    <row r="82" spans="1:13" ht="15.75"/>
-    <row r="85" spans="1:13" ht="15.75"/>
-    <row r="86" spans="1:13" ht="16.5">
+    <row r="86" spans="1:13" ht="17">
       <c r="M86" s="14"/>
     </row>
-    <row r="87" spans="1:13" ht="16.5">
+    <row r="87" spans="1:13" ht="17">
       <c r="M87" s="15"/>
     </row>
-    <row r="90" spans="1:13" ht="15.75"/>
-    <row r="91" spans="1:13" ht="20.25">
+    <row r="91" spans="1:13" ht="20">
       <c r="A91" s="13" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="92" spans="1:13" ht="16.5">
+    <row r="92" spans="1:13" ht="17">
       <c r="A92" s="14" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="93" spans="1:13" ht="16.5">
+    <row r="93" spans="1:13" ht="17">
       <c r="A93" s="15">
         <v>0.17460000000000001</v>
       </c>
     </row>
-    <row r="95" spans="1:13" ht="20.25">
+    <row r="95" spans="1:13" ht="20">
       <c r="A95" s="13" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="96" spans="1:13" ht="16.5">
+    <row r="96" spans="1:13" ht="17">
       <c r="A96" s="14" t="s">
         <v>78</v>
       </c>
@@ -36286,7 +36242,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="101" spans="1:11" ht="32.1">
+    <row r="101" spans="1:11" ht="32">
       <c r="A101" s="1" t="s">
         <v>0</v>
       </c>
@@ -37045,10 +37001,6 @@
         <v>74</v>
       </c>
     </row>
-    <row r="141" spans="1:5" ht="15.75"/>
-    <row r="144" spans="1:5" ht="15.75"/>
-    <row r="176" ht="15.75"/>
-    <row r="178" ht="15.75"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -37057,10 +37009,10 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3570A80-AD87-2A4F-A758-929B3D5D522D}">
-  <dimension ref="A1:K202"/>
-  <sheetFormatPr defaultColWidth="10.625" defaultRowHeight="15.95"/>
+  <dimension ref="A1:K153"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.58203125" defaultRowHeight="16"/>
   <sheetData>
-    <row r="1" spans="1:7" ht="32.1">
+    <row r="1" spans="1:7" ht="32">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -37502,12 +37454,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="20.100000000000001">
+    <row r="22" spans="1:7" ht="20">
       <c r="A22" s="13" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.5">
+    <row r="23" spans="1:7" ht="17">
       <c r="A23" s="14" t="s">
         <v>20</v>
       </c>
@@ -37530,7 +37482,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.5">
+    <row r="24" spans="1:7" ht="17">
       <c r="A24" s="14" t="s">
         <v>5</v>
       </c>
@@ -37553,13 +37505,12 @@
         <v>169</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="15.75"/>
-    <row r="26" spans="1:7" ht="20.25">
+    <row r="26" spans="1:7" ht="20">
       <c r="A26" s="13" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="16.5">
+    <row r="27" spans="1:7" ht="17">
       <c r="A27" s="14" t="s">
         <v>20</v>
       </c>
@@ -37582,7 +37533,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="16.5">
+    <row r="28" spans="1:7" ht="17">
       <c r="A28" s="14" t="s">
         <v>6</v>
       </c>
@@ -37610,12 +37561,12 @@
         <v>28</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="20.100000000000001">
+    <row r="32" spans="1:7" ht="20">
       <c r="A32" s="13" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="17.100000000000001">
+    <row r="33" spans="1:8" ht="17">
       <c r="A33" s="14" t="s">
         <v>30</v>
       </c>
@@ -37627,7 +37578,7 @@
       <c r="E33" s="14"/>
       <c r="F33" s="14"/>
     </row>
-    <row r="34" spans="1:8" ht="17.100000000000001">
+    <row r="34" spans="1:8" ht="17">
       <c r="A34" s="14">
         <v>7</v>
       </c>
@@ -37639,7 +37590,7 @@
       <c r="E34" s="14"/>
       <c r="F34" s="14"/>
     </row>
-    <row r="36" spans="1:8" ht="32.1">
+    <row r="36" spans="1:8" ht="32">
       <c r="A36" s="1" t="s">
         <v>0</v>
       </c>
@@ -38079,7 +38030,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="56" spans="1:7" ht="32.1">
+    <row r="56" spans="1:7" ht="32">
       <c r="A56" s="1" t="s">
         <v>0</v>
       </c>
@@ -38506,7 +38457,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="77" spans="1:7" ht="20.100000000000001">
+    <row r="77" spans="1:7" ht="20">
       <c r="A77" s="10" t="s">
         <v>33</v>
       </c>
@@ -38514,7 +38465,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="78" spans="1:7" ht="20.100000000000001">
+    <row r="78" spans="1:7" ht="20">
       <c r="A78" s="33">
         <v>17</v>
       </c>
@@ -38522,7 +38473,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="79" spans="1:7" ht="20.100000000000001">
+    <row r="79" spans="1:7" ht="20">
       <c r="A79" s="10" t="s">
         <v>76</v>
       </c>
@@ -38530,7 +38481,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="80" spans="1:7" ht="20.100000000000001">
+    <row r="80" spans="1:7" ht="20">
       <c r="A80" s="10">
         <v>1</v>
       </c>
@@ -38538,7 +38489,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:4" ht="20.100000000000001">
+    <row r="81" spans="1:4" ht="20">
       <c r="A81" s="10" t="s">
         <v>34</v>
       </c>
@@ -38546,7 +38497,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="82" spans="1:4" ht="20.100000000000001">
+    <row r="82" spans="1:4" ht="20">
       <c r="A82" s="10" t="s">
         <v>0</v>
       </c>
@@ -38554,7 +38505,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:4" ht="20.100000000000001">
+    <row r="83" spans="1:4" ht="20">
       <c r="A83" s="10"/>
       <c r="D83" s="10"/>
     </row>
@@ -38563,36 +38514,27 @@
         <v>79</v>
       </c>
     </row>
-    <row r="90" spans="1:4" ht="15.75"/>
-    <row r="91" spans="1:4" ht="15.75"/>
-    <row r="92" spans="1:4" ht="15.75"/>
-    <row r="93" spans="1:4" ht="15.75"/>
-    <row r="96" spans="1:4" ht="15.75"/>
-    <row r="97" spans="1:11" ht="15.75"/>
-    <row r="98" spans="1:11" ht="15.75"/>
-    <row r="99" spans="1:11" ht="15.75"/>
-    <row r="100" spans="1:11" ht="20.25">
+    <row r="100" spans="1:11" ht="20">
       <c r="A100" s="13" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="101" spans="1:11" ht="16.5">
+    <row r="101" spans="1:11" ht="17">
       <c r="A101" s="14" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="102" spans="1:11" ht="16.5">
+    <row r="102" spans="1:11" ht="17">
       <c r="A102" s="15">
         <v>0.74490000000000001</v>
       </c>
     </row>
-    <row r="103" spans="1:11" ht="15.75"/>
-    <row r="105" spans="1:11" ht="20.25">
+    <row r="105" spans="1:11" ht="20">
       <c r="A105" s="13" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="106" spans="1:11" ht="16.5">
+    <row r="106" spans="1:11" ht="17">
       <c r="A106" s="14" t="s">
         <v>80</v>
       </c>
@@ -38602,7 +38544,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="110" spans="1:11" ht="32.1">
+    <row r="110" spans="1:11" ht="32">
       <c r="A110" s="1" t="s">
         <v>0</v>
       </c>
@@ -39504,13 +39446,6 @@
         <v>74</v>
       </c>
     </row>
-    <row r="154" spans="1:5" ht="15.75"/>
-    <row r="155" spans="1:5" ht="15.75"/>
-    <row r="157" spans="1:5" ht="15.75"/>
-    <row r="197" ht="15.75"/>
-    <row r="198" ht="15.75"/>
-    <row r="200" ht="15.75"/>
-    <row r="202" ht="15.75"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -39519,10 +39454,10 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DF4D549-59D3-0A4D-A462-1BF22F5BA246}">
-  <dimension ref="A1:K999"/>
-  <sheetFormatPr defaultColWidth="10.625" defaultRowHeight="15.95"/>
+  <dimension ref="A1:K972"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.58203125" defaultRowHeight="16"/>
   <sheetData>
-    <row r="1" spans="1:7" ht="32.1">
+    <row r="1" spans="1:7" ht="32">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -40470,12 +40405,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="44" spans="1:7" ht="20.100000000000001">
+    <row r="44" spans="1:7" ht="20">
       <c r="A44" s="13" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="45" spans="1:7" ht="16.5">
+    <row r="45" spans="1:7" ht="17">
       <c r="A45" s="14" t="s">
         <v>20</v>
       </c>
@@ -40498,7 +40433,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="46" spans="1:7" ht="16.5">
+    <row r="46" spans="1:7" ht="17">
       <c r="A46" s="14" t="s">
         <v>5</v>
       </c>
@@ -40521,12 +40456,12 @@
         <v>779</v>
       </c>
     </row>
-    <row r="48" spans="1:7" ht="20.100000000000001">
+    <row r="48" spans="1:7" ht="20">
       <c r="A48" s="13" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="49" spans="1:7" ht="16.5">
+    <row r="49" spans="1:7" ht="17">
       <c r="A49" s="14" t="s">
         <v>20</v>
       </c>
@@ -40549,7 +40484,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="50" spans="1:7" ht="16.5">
+    <row r="50" spans="1:7" ht="17">
       <c r="A50" s="14" t="s">
         <v>6</v>
       </c>
@@ -40577,12 +40512,12 @@
         <v>28</v>
       </c>
     </row>
-    <row r="53" spans="1:7" ht="20.100000000000001">
+    <row r="53" spans="1:7" ht="20">
       <c r="A53" s="13" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="54" spans="1:7" ht="17.100000000000001">
+    <row r="54" spans="1:7" ht="17">
       <c r="A54" s="14" t="s">
         <v>30</v>
       </c>
@@ -40595,7 +40530,7 @@
       <c r="F54" s="14"/>
       <c r="G54" s="14"/>
     </row>
-    <row r="55" spans="1:7" ht="17.100000000000001">
+    <row r="55" spans="1:7" ht="17">
       <c r="A55" s="14">
         <v>4</v>
       </c>
@@ -40608,7 +40543,7 @@
       <c r="F55" s="14"/>
       <c r="G55" s="14"/>
     </row>
-    <row r="56" spans="1:7" ht="17.100000000000001">
+    <row r="56" spans="1:7" ht="17">
       <c r="A56" s="14">
         <v>32</v>
       </c>
@@ -40621,7 +40556,7 @@
       <c r="F56" s="14"/>
       <c r="G56" s="14"/>
     </row>
-    <row r="57" spans="1:7" ht="17.100000000000001">
+    <row r="57" spans="1:7" ht="17">
       <c r="A57" s="14">
         <v>39</v>
       </c>
@@ -40634,7 +40569,7 @@
       <c r="F57" s="14"/>
       <c r="G57" s="14"/>
     </row>
-    <row r="58" spans="1:7" ht="17.100000000000001">
+    <row r="58" spans="1:7" ht="17">
       <c r="A58" s="14">
         <v>40</v>
       </c>
@@ -40647,10 +40582,10 @@
       <c r="F58" s="14"/>
       <c r="G58" s="14"/>
     </row>
-    <row r="59" spans="1:7" ht="17.100000000000001">
+    <row r="59" spans="1:7" ht="17">
       <c r="A59" s="16"/>
     </row>
-    <row r="61" spans="1:7" ht="32.1">
+    <row r="61" spans="1:7" ht="32">
       <c r="A61" s="1" t="s">
         <v>0</v>
       </c>
@@ -41605,7 +41540,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="104" spans="1:8" ht="32.1">
+    <row r="104" spans="1:8" ht="32">
       <c r="A104" s="1" t="s">
         <v>0</v>
       </c>
@@ -42461,12 +42396,12 @@
         <v>28</v>
       </c>
     </row>
-    <row r="143" spans="1:7" ht="20.100000000000001">
+    <row r="143" spans="1:7" ht="20">
       <c r="A143" s="13" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="144" spans="1:7" ht="17.100000000000001">
+    <row r="144" spans="1:7" ht="17">
       <c r="A144" s="14" t="s">
         <v>30</v>
       </c>
@@ -42479,7 +42414,7 @@
       <c r="F144" s="14"/>
       <c r="G144" s="14"/>
     </row>
-    <row r="145" spans="1:7" ht="17.100000000000001">
+    <row r="145" spans="1:7" ht="17">
       <c r="A145" s="14">
         <v>12</v>
       </c>
@@ -42492,7 +42427,7 @@
       <c r="F145" s="14"/>
       <c r="G145" s="14"/>
     </row>
-    <row r="146" spans="1:7" ht="17.100000000000001">
+    <row r="146" spans="1:7" ht="17">
       <c r="A146" s="14">
         <v>35</v>
       </c>
@@ -42505,7 +42440,7 @@
       <c r="F146" s="14"/>
       <c r="G146" s="14"/>
     </row>
-    <row r="147" spans="1:7" ht="17.100000000000001">
+    <row r="147" spans="1:7" ht="17">
       <c r="A147" s="14">
         <v>36</v>
       </c>
@@ -42518,7 +42453,7 @@
       <c r="F147" s="14"/>
       <c r="G147" s="14"/>
     </row>
-    <row r="149" spans="1:7" ht="32.1">
+    <row r="149" spans="1:7" ht="32">
       <c r="A149" s="1" t="s">
         <v>0</v>
       </c>
@@ -43378,7 +43313,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="188" spans="1:8" ht="32.1">
+    <row r="188" spans="1:8" ht="32">
       <c r="A188" s="1" t="s">
         <v>0</v>
       </c>
@@ -44165,12 +44100,12 @@
         <v>28</v>
       </c>
     </row>
-    <row r="224" spans="1:7" ht="20.100000000000001">
+    <row r="224" spans="1:7" ht="20">
       <c r="A224" s="13" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="225" spans="1:7" ht="17.100000000000001">
+    <row r="225" spans="1:7" ht="17">
       <c r="A225" s="14" t="s">
         <v>30</v>
       </c>
@@ -44183,7 +44118,7 @@
       <c r="F225" s="14"/>
       <c r="G225" s="14"/>
     </row>
-    <row r="226" spans="1:7" ht="17.100000000000001">
+    <row r="226" spans="1:7" ht="17">
       <c r="A226" s="14">
         <v>29</v>
       </c>
@@ -44196,7 +44131,7 @@
       <c r="F226" s="14"/>
       <c r="G226" s="14"/>
     </row>
-    <row r="227" spans="1:7" ht="17.100000000000001">
+    <row r="227" spans="1:7" ht="17">
       <c r="A227" s="14">
         <v>32</v>
       </c>
@@ -44209,7 +44144,7 @@
       <c r="F227" s="14"/>
       <c r="G227" s="14"/>
     </row>
-    <row r="228" spans="1:7" ht="17.100000000000001">
+    <row r="228" spans="1:7" ht="17">
       <c r="A228" s="14">
         <v>33</v>
       </c>
@@ -44222,10 +44157,10 @@
       <c r="F228" s="14"/>
       <c r="G228" s="14"/>
     </row>
-    <row r="229" spans="1:7" ht="17.100000000000001">
+    <row r="229" spans="1:7" ht="17">
       <c r="A229" s="16"/>
     </row>
-    <row r="231" spans="1:7" ht="32.1">
+    <row r="231" spans="1:7" ht="32">
       <c r="A231" s="1" t="s">
         <v>0</v>
       </c>
@@ -45016,7 +44951,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="267" spans="1:8" ht="32.1">
+    <row r="267" spans="1:8" ht="32">
       <c r="A267" s="1" t="s">
         <v>0</v>
       </c>
@@ -45734,12 +45669,12 @@
         <v>28</v>
       </c>
     </row>
-    <row r="301" spans="1:7" ht="20.100000000000001">
+    <row r="301" spans="1:7" ht="20">
       <c r="A301" s="13" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="302" spans="1:7" ht="17.100000000000001">
+    <row r="302" spans="1:7" ht="17">
       <c r="A302" s="14" t="s">
         <v>30</v>
       </c>
@@ -45752,7 +45687,7 @@
       <c r="F302" s="14"/>
       <c r="G302" s="14"/>
     </row>
-    <row r="303" spans="1:7" ht="17.100000000000001">
+    <row r="303" spans="1:7" ht="17">
       <c r="A303" s="14">
         <v>18</v>
       </c>
@@ -45765,7 +45700,7 @@
       <c r="F303" s="14"/>
       <c r="G303" s="14"/>
     </row>
-    <row r="304" spans="1:7" ht="17.100000000000001">
+    <row r="304" spans="1:7" ht="17">
       <c r="A304" s="14">
         <v>29</v>
       </c>
@@ -45778,7 +45713,7 @@
       <c r="F304" s="14"/>
       <c r="G304" s="14"/>
     </row>
-    <row r="305" spans="1:7" ht="17.100000000000001">
+    <row r="305" spans="1:7" ht="17">
       <c r="A305" s="14">
         <v>30</v>
       </c>
@@ -45791,7 +45726,7 @@
       <c r="F305" s="14"/>
       <c r="G305" s="14"/>
     </row>
-    <row r="307" spans="1:7" ht="32.1">
+    <row r="307" spans="1:7" ht="32">
       <c r="A307" s="1" t="s">
         <v>0</v>
       </c>
@@ -46513,7 +46448,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="340" spans="1:8" ht="32.1">
+    <row r="340" spans="1:8" ht="32">
       <c r="A340" s="1" t="s">
         <v>0</v>
       </c>
@@ -47162,12 +47097,12 @@
         <v>28</v>
       </c>
     </row>
-    <row r="370" spans="1:8" ht="20.100000000000001">
+    <row r="370" spans="1:8" ht="20">
       <c r="A370" s="13" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="371" spans="1:8" ht="17.100000000000001">
+    <row r="371" spans="1:8" ht="17">
       <c r="A371" s="14" t="s">
         <v>30</v>
       </c>
@@ -47180,7 +47115,7 @@
       <c r="F371" s="14"/>
       <c r="G371" s="14"/>
     </row>
-    <row r="372" spans="1:8" ht="17.100000000000001">
+    <row r="372" spans="1:8" ht="17">
       <c r="A372" s="14">
         <v>6</v>
       </c>
@@ -47193,7 +47128,7 @@
       <c r="F372" s="14"/>
       <c r="G372" s="14"/>
     </row>
-    <row r="373" spans="1:8" ht="17.100000000000001">
+    <row r="373" spans="1:8" ht="17">
       <c r="A373" s="14">
         <v>27</v>
       </c>
@@ -47206,7 +47141,7 @@
       <c r="F373" s="14"/>
       <c r="G373" s="14"/>
     </row>
-    <row r="375" spans="1:8" ht="32.1">
+    <row r="375" spans="1:8" ht="32">
       <c r="A375" s="1" t="s">
         <v>0</v>
       </c>
@@ -47856,7 +47791,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="405" spans="1:8" ht="32.1">
+    <row r="405" spans="1:8" ht="32">
       <c r="A405" s="1" t="s">
         <v>0</v>
       </c>
@@ -48459,12 +48394,12 @@
         <v>28</v>
       </c>
     </row>
-    <row r="434" spans="1:7" ht="20.100000000000001">
+    <row r="434" spans="1:7" ht="20">
       <c r="A434" s="13" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="435" spans="1:7" ht="17.100000000000001">
+    <row r="435" spans="1:7" ht="17">
       <c r="A435" s="14" t="s">
         <v>30</v>
       </c>
@@ -48476,7 +48411,7 @@
       <c r="E435" s="14"/>
       <c r="F435" s="14"/>
     </row>
-    <row r="436" spans="1:7" ht="17.100000000000001">
+    <row r="436" spans="1:7" ht="17">
       <c r="A436" s="14">
         <v>12</v>
       </c>
@@ -48488,7 +48423,7 @@
       <c r="E436" s="14"/>
       <c r="F436" s="14"/>
     </row>
-    <row r="438" spans="1:7" ht="32.1">
+    <row r="438" spans="1:7" ht="32">
       <c r="A438" s="1" t="s">
         <v>0</v>
       </c>
@@ -49089,7 +49024,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="466" spans="1:7" ht="32.1">
+    <row r="466" spans="1:7" ht="32">
       <c r="A466" s="1" t="s">
         <v>0</v>
       </c>
@@ -49669,12 +49604,12 @@
         <v>28</v>
       </c>
     </row>
-    <row r="493" spans="1:7" ht="20.100000000000001">
+    <row r="493" spans="1:7" ht="20">
       <c r="A493" s="13" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="494" spans="1:7" ht="17.100000000000001">
+    <row r="494" spans="1:7" ht="17">
       <c r="A494" s="14" t="s">
         <v>30</v>
       </c>
@@ -49686,7 +49621,7 @@
       <c r="E494" s="14"/>
       <c r="F494" s="14"/>
     </row>
-    <row r="495" spans="1:7" ht="17.100000000000001">
+    <row r="495" spans="1:7" ht="17">
       <c r="A495" s="14">
         <v>21</v>
       </c>
@@ -49698,7 +49633,7 @@
       <c r="E495" s="14"/>
       <c r="F495" s="14"/>
     </row>
-    <row r="497" spans="1:7" ht="32.1">
+    <row r="497" spans="1:7" ht="32">
       <c r="A497" s="1" t="s">
         <v>0</v>
       </c>
@@ -50276,7 +50211,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="523" spans="1:8" ht="32.1">
+    <row r="523" spans="1:8" ht="32">
       <c r="A523" s="1" t="s">
         <v>0</v>
       </c>
@@ -50833,12 +50768,12 @@
         <v>28</v>
       </c>
     </row>
-    <row r="549" spans="1:7" ht="20.100000000000001">
+    <row r="549" spans="1:7" ht="20">
       <c r="A549" s="13" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="550" spans="1:7" ht="17.100000000000001">
+    <row r="550" spans="1:7" ht="17">
       <c r="A550" s="14" t="s">
         <v>30</v>
       </c>
@@ -50851,7 +50786,7 @@
       <c r="F550" s="14"/>
       <c r="G550" s="14"/>
     </row>
-    <row r="551" spans="1:7" ht="17.100000000000001">
+    <row r="551" spans="1:7" ht="17">
       <c r="A551" s="14">
         <v>21</v>
       </c>
@@ -50864,7 +50799,7 @@
       <c r="F551" s="14"/>
       <c r="G551" s="14"/>
     </row>
-    <row r="552" spans="1:7" ht="17.100000000000001">
+    <row r="552" spans="1:7" ht="17">
       <c r="A552" s="14">
         <v>23</v>
       </c>
@@ -50877,7 +50812,7 @@
       <c r="F552" s="14"/>
       <c r="G552" s="14"/>
     </row>
-    <row r="554" spans="1:7" ht="32.1">
+    <row r="554" spans="1:7" ht="32">
       <c r="A554" s="1" t="s">
         <v>0</v>
       </c>
@@ -51435,7 +51370,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="580" spans="1:8" ht="32.1">
+    <row r="580" spans="1:8" ht="32">
       <c r="A580" s="1" t="s">
         <v>0</v>
       </c>
@@ -51946,12 +51881,12 @@
         <v>28</v>
       </c>
     </row>
-    <row r="604" spans="1:7" ht="20.100000000000001">
+    <row r="604" spans="1:7" ht="20">
       <c r="A604" s="13" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="605" spans="1:7" ht="17.100000000000001">
+    <row r="605" spans="1:7" ht="17">
       <c r="A605" s="14" t="s">
         <v>30</v>
       </c>
@@ -51963,7 +51898,7 @@
       <c r="E605" s="14"/>
       <c r="F605" s="14"/>
     </row>
-    <row r="606" spans="1:7" ht="17.100000000000001">
+    <row r="606" spans="1:7" ht="17">
       <c r="A606" s="14">
         <v>15</v>
       </c>
@@ -51975,7 +51910,7 @@
       <c r="E606" s="14"/>
       <c r="F606" s="14"/>
     </row>
-    <row r="607" spans="1:7" ht="17.100000000000001">
+    <row r="607" spans="1:7" ht="17">
       <c r="A607" s="14">
         <v>21</v>
       </c>
@@ -51987,7 +51922,7 @@
       <c r="E607" s="14"/>
       <c r="F607" s="14"/>
     </row>
-    <row r="609" spans="1:8" ht="32.1">
+    <row r="609" spans="1:8" ht="32">
       <c r="A609" s="1" t="s">
         <v>0</v>
       </c>
@@ -52499,7 +52434,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="633" spans="1:8" ht="32.1">
+    <row r="633" spans="1:8" ht="32">
       <c r="A633" s="1" t="s">
         <v>0</v>
       </c>
@@ -52964,12 +52899,12 @@
         <v>28</v>
       </c>
     </row>
-    <row r="655" spans="1:7" ht="20.100000000000001">
+    <row r="655" spans="1:7" ht="20">
       <c r="A655" s="13" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="656" spans="1:7" ht="17.100000000000001">
+    <row r="656" spans="1:7" ht="17">
       <c r="A656" s="14" t="s">
         <v>30</v>
       </c>
@@ -52981,7 +52916,7 @@
       <c r="E656" s="14"/>
       <c r="F656" s="14"/>
     </row>
-    <row r="657" spans="1:7" ht="17.100000000000001">
+    <row r="657" spans="1:7" ht="17">
       <c r="A657" s="14">
         <v>17</v>
       </c>
@@ -52993,7 +52928,7 @@
       <c r="E657" s="14"/>
       <c r="F657" s="14"/>
     </row>
-    <row r="659" spans="1:7" ht="32.1">
+    <row r="659" spans="1:7" ht="32">
       <c r="A659" s="1" t="s">
         <v>0</v>
       </c>
@@ -53456,7 +53391,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="681" spans="1:8" ht="32.1">
+    <row r="681" spans="1:8" ht="32">
       <c r="A681" s="1" t="s">
         <v>0</v>
       </c>
@@ -53898,12 +53833,12 @@
         <v>28</v>
       </c>
     </row>
-    <row r="702" spans="1:7" ht="20.100000000000001">
+    <row r="702" spans="1:7" ht="20">
       <c r="A702" s="13" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="703" spans="1:7" ht="17.100000000000001">
+    <row r="703" spans="1:7" ht="17">
       <c r="A703" s="14" t="s">
         <v>30</v>
       </c>
@@ -53915,7 +53850,7 @@
       <c r="E703" s="14"/>
       <c r="F703" s="14"/>
     </row>
-    <row r="704" spans="1:7" ht="17.100000000000001">
+    <row r="704" spans="1:7" ht="17">
       <c r="A704" s="14">
         <v>2</v>
       </c>
@@ -53927,7 +53862,7 @@
       <c r="E704" s="14"/>
       <c r="F704" s="14"/>
     </row>
-    <row r="705" spans="1:8" ht="17.100000000000001">
+    <row r="705" spans="1:8" ht="17">
       <c r="A705" s="14">
         <v>7</v>
       </c>
@@ -53939,7 +53874,7 @@
       <c r="E705" s="14"/>
       <c r="F705" s="14"/>
     </row>
-    <row r="707" spans="1:8" ht="32.1">
+    <row r="707" spans="1:8" ht="32">
       <c r="A707" s="1" t="s">
         <v>0</v>
       </c>
@@ -54382,7 +54317,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="727" spans="1:7" ht="32.1">
+    <row r="727" spans="1:7" ht="32">
       <c r="A727" s="1" t="s">
         <v>0</v>
       </c>
@@ -54778,12 +54713,12 @@
         <v>28</v>
       </c>
     </row>
-    <row r="746" spans="1:7" ht="20.100000000000001">
+    <row r="746" spans="1:7" ht="20">
       <c r="A746" s="13" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="747" spans="1:7" ht="17.100000000000001">
+    <row r="747" spans="1:7" ht="17">
       <c r="A747" s="14" t="s">
         <v>30</v>
       </c>
@@ -54795,7 +54730,7 @@
       <c r="E747" s="14"/>
       <c r="F747" s="14"/>
     </row>
-    <row r="748" spans="1:7" ht="17.100000000000001">
+    <row r="748" spans="1:7" ht="17">
       <c r="A748" s="14">
         <v>16</v>
       </c>
@@ -54807,7 +54742,7 @@
       <c r="E748" s="14"/>
       <c r="F748" s="14"/>
     </row>
-    <row r="750" spans="1:7" ht="32.1">
+    <row r="750" spans="1:7" ht="32">
       <c r="A750" s="1" t="s">
         <v>0</v>
       </c>
@@ -55201,7 +55136,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="768" spans="1:8" ht="32.1">
+    <row r="768" spans="1:8" ht="32">
       <c r="A768" s="1" t="s">
         <v>0</v>
       </c>
@@ -55574,12 +55509,12 @@
         <v>28</v>
       </c>
     </row>
-    <row r="786" spans="1:8" ht="20.100000000000001">
+    <row r="786" spans="1:8" ht="20">
       <c r="A786" s="13" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="787" spans="1:8" ht="17.100000000000001">
+    <row r="787" spans="1:8" ht="17">
       <c r="A787" s="14" t="s">
         <v>30</v>
       </c>
@@ -55591,7 +55526,7 @@
       <c r="E787" s="14"/>
       <c r="F787" s="14"/>
     </row>
-    <row r="788" spans="1:8" ht="17.100000000000001">
+    <row r="788" spans="1:8" ht="17">
       <c r="A788" s="14">
         <v>2</v>
       </c>
@@ -55603,7 +55538,7 @@
       <c r="E788" s="14"/>
       <c r="F788" s="14"/>
     </row>
-    <row r="790" spans="1:8" ht="32.1">
+    <row r="790" spans="1:8" ht="32">
       <c r="A790" s="1" t="s">
         <v>0</v>
       </c>
@@ -55974,7 +55909,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="808" spans="1:7" ht="32.1">
+    <row r="808" spans="1:7" ht="32">
       <c r="A808" s="1" t="s">
         <v>0</v>
       </c>
@@ -56319,17 +56254,17 @@
         <v>290</v>
       </c>
     </row>
-    <row r="824" spans="1:8" ht="15.75">
+    <row r="824" spans="1:8">
       <c r="A824" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="825" spans="1:8" ht="20.100000000000001">
+    <row r="825" spans="1:8" ht="20">
       <c r="A825" s="13" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="826" spans="1:8" ht="17.100000000000001">
+    <row r="826" spans="1:8" ht="17">
       <c r="A826" s="14" t="s">
         <v>30</v>
       </c>
@@ -56341,7 +56276,7 @@
       <c r="E826" s="14"/>
       <c r="F826" s="14"/>
     </row>
-    <row r="827" spans="1:8" ht="17.100000000000001">
+    <row r="827" spans="1:8" ht="17">
       <c r="A827" s="14">
         <v>3</v>
       </c>
@@ -56353,7 +56288,7 @@
       <c r="E827" s="14"/>
       <c r="F827" s="14"/>
     </row>
-    <row r="829" spans="1:8" ht="32.1">
+    <row r="829" spans="1:8" ht="32">
       <c r="A829" s="1" t="s">
         <v>0</v>
       </c>
@@ -56701,7 +56636,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="846" spans="1:7" ht="32.1">
+    <row r="846" spans="1:7" ht="32">
       <c r="A846" s="1" t="s">
         <v>0</v>
       </c>
@@ -57028,12 +56963,12 @@
         <v>28</v>
       </c>
     </row>
-    <row r="862" spans="1:7" ht="20.100000000000001">
+    <row r="862" spans="1:7" ht="20">
       <c r="A862" s="13" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="863" spans="1:7" ht="17.100000000000001">
+    <row r="863" spans="1:7" ht="17">
       <c r="A863" s="14" t="s">
         <v>30</v>
       </c>
@@ -57045,7 +56980,7 @@
       <c r="E863" s="14"/>
       <c r="F863" s="14"/>
     </row>
-    <row r="864" spans="1:7" ht="17.100000000000001">
+    <row r="864" spans="1:7" ht="17">
       <c r="A864" s="14">
         <v>7</v>
       </c>
@@ -57057,10 +56992,10 @@
       <c r="E864" s="14"/>
       <c r="F864" s="14"/>
     </row>
-    <row r="865" spans="1:8" ht="17.100000000000001">
+    <row r="865" spans="1:8" ht="17">
       <c r="A865" s="16"/>
     </row>
-    <row r="868" spans="1:8" ht="32.1">
+    <row r="868" spans="1:8" ht="32">
       <c r="A868" s="1" t="s">
         <v>0</v>
       </c>
@@ -57385,7 +57320,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="884" spans="1:7" ht="32.1">
+    <row r="884" spans="1:7" ht="32">
       <c r="A884" s="1" t="s">
         <v>0</v>
       </c>
@@ -57697,7 +57632,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="901" spans="1:4" ht="20.100000000000001">
+    <row r="901" spans="1:4" ht="20">
       <c r="A901" s="10" t="s">
         <v>33</v>
       </c>
@@ -57705,7 +57640,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="902" spans="1:4" ht="20.100000000000001">
+    <row r="902" spans="1:4" ht="20">
       <c r="A902" s="33">
         <v>12</v>
       </c>
@@ -57713,7 +57648,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="903" spans="1:4" ht="20.100000000000001">
+    <row r="903" spans="1:4" ht="20">
       <c r="A903" s="10" t="s">
         <v>76</v>
       </c>
@@ -57721,7 +57656,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="904" spans="1:4" ht="20.100000000000001">
+    <row r="904" spans="1:4" ht="20">
       <c r="A904" s="10">
         <v>1</v>
       </c>
@@ -57729,7 +57664,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="905" spans="1:4" ht="20.100000000000001">
+    <row r="905" spans="1:4" ht="20">
       <c r="A905" s="10" t="s">
         <v>34</v>
       </c>
@@ -57737,7 +57672,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="906" spans="1:4" ht="20.100000000000001">
+    <row r="906" spans="1:4" ht="20">
       <c r="A906" s="10" t="s">
         <v>0</v>
       </c>
@@ -57745,11 +57680,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="907" spans="1:4" ht="20.25">
+    <row r="907" spans="1:4" ht="20">
       <c r="A907" s="10"/>
       <c r="D907" s="10"/>
     </row>
-    <row r="908" spans="1:4" ht="20.25">
+    <row r="908" spans="1:4" ht="20">
       <c r="A908" s="10"/>
       <c r="D908" s="10"/>
     </row>
@@ -57758,41 +57693,29 @@
         <v>81</v>
       </c>
     </row>
-    <row r="910" spans="1:4" ht="15.75"/>
-    <row r="911" spans="1:4" ht="15.75"/>
-    <row r="912" spans="1:4" ht="15.75"/>
-    <row r="913" spans="1:2" ht="15.75"/>
-    <row r="914" spans="1:2" ht="15.75"/>
-    <row r="917" spans="1:2" ht="15.75"/>
-    <row r="918" spans="1:2" ht="15.75"/>
-    <row r="919" spans="1:2" ht="15.75"/>
-    <row r="920" spans="1:2" ht="15.75"/>
-    <row r="921" spans="1:2" ht="15.75"/>
-    <row r="922" spans="1:2" ht="15.75"/>
-    <row r="923" spans="1:2" ht="15.75"/>
-    <row r="924" spans="1:2" ht="20.25">
+    <row r="924" spans="1:2" ht="20">
       <c r="A924" s="13" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="925" spans="1:2" ht="16.5">
+    <row r="925" spans="1:2" ht="17">
       <c r="A925" s="14" t="s">
         <v>37</v>
       </c>
       <c r="B925" s="14"/>
     </row>
-    <row r="926" spans="1:2" ht="16.5">
+    <row r="926" spans="1:2" ht="17">
       <c r="A926" s="15">
         <v>0.74219999999999997</v>
       </c>
       <c r="B926" s="15"/>
     </row>
-    <row r="928" spans="1:2" ht="20.25">
+    <row r="928" spans="1:2" ht="20">
       <c r="A928" s="13" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="929" spans="1:11" ht="16.5">
+    <row r="929" spans="1:11" ht="17">
       <c r="A929" s="14" t="s">
         <v>82</v>
       </c>
@@ -57802,7 +57725,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="933" spans="1:11" ht="32.1">
+    <row r="933" spans="1:11" ht="32">
       <c r="A933" s="1" t="s">
         <v>0</v>
       </c>
@@ -58524,10 +58447,6 @@
         <v>74</v>
       </c>
     </row>
-    <row r="973" spans="1:5" ht="15.75"/>
-    <row r="977" ht="15.75"/>
-    <row r="982" ht="15.75"/>
-    <row r="999" ht="15.75"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -58536,10 +58455,10 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14A28B7B-95CA-F946-8320-DDA1F227733F}">
-  <dimension ref="A1:K607"/>
-  <sheetFormatPr defaultColWidth="10.625" defaultRowHeight="15.95"/>
+  <dimension ref="A1:K573"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.58203125" defaultRowHeight="16"/>
   <sheetData>
-    <row r="1" spans="1:7" ht="32.1">
+    <row r="1" spans="1:7" ht="32">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -59579,12 +59498,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="48" spans="1:7" ht="20.100000000000001">
+    <row r="48" spans="1:7" ht="20">
       <c r="A48" s="13" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="49" spans="1:7" ht="16.5">
+    <row r="49" spans="1:7" ht="17">
       <c r="A49" s="14" t="s">
         <v>20</v>
       </c>
@@ -59607,7 +59526,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="50" spans="1:7" ht="16.5">
+    <row r="50" spans="1:7" ht="17">
       <c r="A50" s="14" t="s">
         <v>5</v>
       </c>
@@ -59630,12 +59549,12 @@
         <v>849</v>
       </c>
     </row>
-    <row r="53" spans="1:7" ht="20.100000000000001">
+    <row r="53" spans="1:7" ht="20">
       <c r="A53" s="13" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="54" spans="1:7" ht="16.5">
+    <row r="54" spans="1:7" ht="17">
       <c r="A54" s="14" t="s">
         <v>20</v>
       </c>
@@ -59658,7 +59577,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="55" spans="1:7" ht="16.5">
+    <row r="55" spans="1:7" ht="17">
       <c r="A55" s="14" t="s">
         <v>6</v>
       </c>
@@ -59686,12 +59605,12 @@
         <v>28</v>
       </c>
     </row>
-    <row r="59" spans="1:7" ht="20.100000000000001">
+    <row r="59" spans="1:7" ht="20">
       <c r="A59" s="13" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="60" spans="1:7" ht="17.100000000000001">
+    <row r="60" spans="1:7" ht="17">
       <c r="A60" s="14" t="s">
         <v>30</v>
       </c>
@@ -59704,7 +59623,7 @@
       <c r="F60" s="14"/>
       <c r="G60" s="14"/>
     </row>
-    <row r="61" spans="1:7" ht="17.100000000000001">
+    <row r="61" spans="1:7" ht="17">
       <c r="A61" s="14">
         <v>19</v>
       </c>
@@ -59717,7 +59636,7 @@
       <c r="F61" s="14"/>
       <c r="G61" s="14"/>
     </row>
-    <row r="62" spans="1:7" ht="17.100000000000001">
+    <row r="62" spans="1:7" ht="17">
       <c r="A62" s="14">
         <v>27</v>
       </c>
@@ -59730,7 +59649,7 @@
       <c r="F62" s="14"/>
       <c r="G62" s="14"/>
     </row>
-    <row r="63" spans="1:7" ht="17.100000000000001">
+    <row r="63" spans="1:7" ht="17">
       <c r="A63" s="14">
         <v>37</v>
       </c>
@@ -59743,7 +59662,7 @@
       <c r="F63" s="14"/>
       <c r="G63" s="14"/>
     </row>
-    <row r="64" spans="1:7" ht="17.100000000000001">
+    <row r="64" spans="1:7" ht="17">
       <c r="A64" s="14">
         <v>42</v>
       </c>
@@ -59756,7 +59675,7 @@
       <c r="F64" s="14"/>
       <c r="G64" s="14"/>
     </row>
-    <row r="65" spans="1:7" ht="17.100000000000001">
+    <row r="65" spans="1:7" ht="17">
       <c r="A65" s="14">
         <v>44</v>
       </c>
@@ -59769,10 +59688,10 @@
       <c r="F65" s="14"/>
       <c r="G65" s="14"/>
     </row>
-    <row r="66" spans="1:7" ht="17.100000000000001">
+    <row r="66" spans="1:7" ht="17">
       <c r="A66" s="16"/>
     </row>
-    <row r="68" spans="1:7" ht="32.1">
+    <row r="68" spans="1:7" ht="32">
       <c r="A68" s="1" t="s">
         <v>0</v>
       </c>
@@ -60822,7 +60741,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="115" spans="1:7" ht="32.1">
+    <row r="115" spans="1:7" ht="32">
       <c r="A115" s="1" t="s">
         <v>0</v>
       </c>
@@ -61747,12 +61666,12 @@
         <v>28</v>
       </c>
     </row>
-    <row r="157" spans="1:7" ht="20.100000000000001">
+    <row r="157" spans="1:7" ht="20">
       <c r="A157" s="13" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="158" spans="1:7" ht="17.100000000000001">
+    <row r="158" spans="1:7" ht="17">
       <c r="A158" s="14" t="s">
         <v>30</v>
       </c>
@@ -61764,7 +61683,7 @@
       <c r="E158" s="14"/>
       <c r="F158" s="14"/>
     </row>
-    <row r="159" spans="1:7" ht="17.100000000000001">
+    <row r="159" spans="1:7" ht="17">
       <c r="A159" s="14">
         <v>39</v>
       </c>
@@ -61776,7 +61695,7 @@
       <c r="E159" s="14"/>
       <c r="F159" s="14"/>
     </row>
-    <row r="161" spans="1:7" ht="32.1">
+    <row r="161" spans="1:7" ht="32">
       <c r="A161" s="1" t="s">
         <v>0</v>
       </c>
@@ -62699,7 +62618,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="203" spans="1:8" ht="32.1">
+    <row r="203" spans="1:8" ht="32">
       <c r="A203" s="1" t="s">
         <v>0</v>
       </c>
@@ -63601,12 +63520,12 @@
         <v>28</v>
       </c>
     </row>
-    <row r="244" spans="1:7" ht="20.100000000000001">
+    <row r="244" spans="1:7" ht="20">
       <c r="A244" s="13" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="245" spans="1:7" ht="17.100000000000001">
+    <row r="245" spans="1:7" ht="17">
       <c r="A245" s="14" t="s">
         <v>30</v>
       </c>
@@ -63618,7 +63537,7 @@
       <c r="E245" s="14"/>
       <c r="F245" s="14"/>
     </row>
-    <row r="246" spans="1:7" ht="17.100000000000001">
+    <row r="246" spans="1:7" ht="17">
       <c r="A246" s="14">
         <v>36</v>
       </c>
@@ -63630,7 +63549,7 @@
       <c r="E246" s="14"/>
       <c r="F246" s="14"/>
     </row>
-    <row r="247" spans="1:7" ht="17.100000000000001">
+    <row r="247" spans="1:7" ht="17">
       <c r="A247" s="14">
         <v>38</v>
       </c>
@@ -63642,10 +63561,10 @@
       <c r="E247" s="14"/>
       <c r="F247" s="14"/>
     </row>
-    <row r="248" spans="1:7" ht="17.100000000000001">
+    <row r="248" spans="1:7" ht="17">
       <c r="A248" s="16"/>
     </row>
-    <row r="250" spans="1:7" ht="32.1">
+    <row r="250" spans="1:7" ht="32">
       <c r="A250" s="1" t="s">
         <v>0</v>
       </c>
@@ -64548,7 +64467,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="291" spans="1:7" ht="32.1">
+    <row r="291" spans="1:7" ht="32">
       <c r="A291" s="1" t="s">
         <v>0</v>
       </c>
@@ -65404,12 +65323,12 @@
         <v>28</v>
       </c>
     </row>
-    <row r="330" spans="1:7" ht="20.100000000000001">
+    <row r="330" spans="1:7" ht="20">
       <c r="A330" s="13" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="331" spans="1:7" ht="17.100000000000001">
+    <row r="331" spans="1:7" ht="17">
       <c r="A331" s="14" t="s">
         <v>30</v>
       </c>
@@ -65422,7 +65341,7 @@
       <c r="F331" s="14"/>
       <c r="G331" s="14"/>
     </row>
-    <row r="332" spans="1:7" ht="17.100000000000001">
+    <row r="332" spans="1:7" ht="17">
       <c r="A332" s="14">
         <v>9</v>
       </c>
@@ -65435,7 +65354,7 @@
       <c r="F332" s="14"/>
       <c r="G332" s="14"/>
     </row>
-    <row r="333" spans="1:7" ht="17.100000000000001">
+    <row r="333" spans="1:7" ht="17">
       <c r="A333" s="14">
         <v>20</v>
       </c>
@@ -65448,7 +65367,7 @@
       <c r="F333" s="14"/>
       <c r="G333" s="14"/>
     </row>
-    <row r="334" spans="1:7" ht="17.100000000000001">
+    <row r="334" spans="1:7" ht="17">
       <c r="A334" s="14">
         <v>35</v>
       </c>
@@ -65461,7 +65380,7 @@
       <c r="F334" s="14"/>
       <c r="G334" s="14"/>
     </row>
-    <row r="335" spans="1:7" ht="17.100000000000001">
+    <row r="335" spans="1:7" ht="17">
       <c r="A335" s="14">
         <v>36</v>
       </c>
@@ -65474,7 +65393,7 @@
       <c r="F335" s="14"/>
       <c r="G335" s="14"/>
     </row>
-    <row r="337" spans="1:8" ht="32.1">
+    <row r="337" spans="1:8" ht="32">
       <c r="A337" s="1" t="s">
         <v>0</v>
       </c>
@@ -66337,7 +66256,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="376" spans="1:8" ht="32.1">
+    <row r="376" spans="1:8" ht="32">
       <c r="A376" s="1" t="s">
         <v>0</v>
       </c>
@@ -67096,17 +67015,17 @@
         <v>1305</v>
       </c>
     </row>
-    <row r="410" spans="1:7" ht="15.75">
+    <row r="410" spans="1:7">
       <c r="A410" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="411" spans="1:7" ht="20.100000000000001">
+    <row r="411" spans="1:7" ht="20">
       <c r="A411" s="13" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="412" spans="1:7" ht="17.100000000000001">
+    <row r="412" spans="1:7" ht="17">
       <c r="A412" s="14" t="s">
         <v>30</v>
       </c>
@@ -67118,7 +67037,7 @@
       <c r="E412" s="14"/>
       <c r="F412" s="14"/>
     </row>
-    <row r="413" spans="1:7" ht="17.100000000000001">
+    <row r="413" spans="1:7" ht="17">
       <c r="A413" s="14">
         <v>20</v>
       </c>
@@ -67130,7 +67049,7 @@
       <c r="E413" s="14"/>
       <c r="F413" s="14"/>
     </row>
-    <row r="415" spans="1:7" ht="32.1">
+    <row r="415" spans="1:7" ht="32">
       <c r="A415" s="1" t="s">
         <v>0</v>
       </c>
@@ -67892,7 +67811,7 @@
         <v>1305</v>
       </c>
     </row>
-    <row r="450" spans="1:7" ht="32.1">
+    <row r="450" spans="1:7" ht="32">
       <c r="A450" s="1" t="s">
         <v>0</v>
       </c>
@@ -68641,7 +68560,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="485" spans="1:7" ht="20.100000000000001">
+    <row r="485" spans="1:7" ht="20">
       <c r="A485" s="10" t="s">
         <v>33</v>
       </c>
@@ -68649,7 +68568,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="486" spans="1:7" ht="20.100000000000001">
+    <row r="486" spans="1:7" ht="20">
       <c r="A486" s="33">
         <v>31</v>
       </c>
@@ -68657,7 +68576,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="487" spans="1:7" ht="20.100000000000001">
+    <row r="487" spans="1:7" ht="20">
       <c r="A487" s="10" t="s">
         <v>76</v>
       </c>
@@ -68665,7 +68584,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="488" spans="1:7" ht="20.100000000000001">
+    <row r="488" spans="1:7" ht="20">
       <c r="A488" s="10">
         <v>1</v>
       </c>
@@ -68673,7 +68592,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="489" spans="1:7" ht="20.100000000000001">
+    <row r="489" spans="1:7" ht="20">
       <c r="A489" s="10" t="s">
         <v>34</v>
       </c>
@@ -68681,7 +68600,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="490" spans="1:7" ht="20.100000000000001">
+    <row r="490" spans="1:7" ht="20">
       <c r="A490" s="10" t="s">
         <v>0</v>
       </c>
@@ -68689,49 +68608,37 @@
         <v>0</v>
       </c>
     </row>
-    <row r="492" spans="1:7" ht="15.75"/>
-    <row r="493" spans="1:7" ht="15.75"/>
-    <row r="494" spans="1:7" ht="15.75"/>
-    <row r="495" spans="1:7" ht="15.75"/>
-    <row r="496" spans="1:7" ht="15.75"/>
-    <row r="499" spans="1:11" ht="15.75"/>
-    <row r="500" spans="1:11" ht="15.75"/>
-    <row r="501" spans="1:11" ht="15.75"/>
-    <row r="502" spans="1:11" ht="15.75"/>
-    <row r="503" spans="1:11" ht="15.75"/>
-    <row r="504" spans="1:11" ht="20.25">
+    <row r="504" spans="1:11" ht="20">
       <c r="A504" s="13" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="505" spans="1:11" ht="16.5">
+    <row r="505" spans="1:11" ht="17">
       <c r="A505" s="14" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="506" spans="1:11" ht="16.5">
+    <row r="506" spans="1:11" ht="17">
       <c r="A506" s="15">
         <v>0.82330000000000003</v>
       </c>
     </row>
-    <row r="507" spans="1:11" ht="15.75"/>
-    <row r="508" spans="1:11" ht="20.25">
+    <row r="508" spans="1:11" ht="20">
       <c r="A508" s="13" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="509" spans="1:11" ht="16.5">
+    <row r="509" spans="1:11" ht="17">
       <c r="A509" s="14" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="510" spans="1:11" ht="15.75"/>
     <row r="511" spans="1:11">
       <c r="A511" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="512" spans="1:11" ht="32.1">
+    <row r="512" spans="1:11" ht="32">
       <c r="A512" s="1" t="s">
         <v>0</v>
       </c>
@@ -70138,11 +70045,6 @@
         <v>74</v>
       </c>
     </row>
-    <row r="576" spans="1:5" ht="15.75"/>
-    <row r="600" ht="15.75"/>
-    <row r="601" ht="15.75"/>
-    <row r="605" ht="15.75"/>
-    <row r="607" ht="15.75"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -70152,10 +70054,10 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4B1F58C-C214-7241-A21F-8EFC79D6D51C}">
-  <dimension ref="A1:K242"/>
-  <sheetFormatPr defaultColWidth="10.625" defaultRowHeight="15.95"/>
+  <dimension ref="A1:K208"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.58203125" defaultRowHeight="16"/>
   <sheetData>
-    <row r="1" spans="1:7" ht="32.1">
+    <row r="1" spans="1:7" ht="32">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -70643,12 +70545,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="20.100000000000001">
+    <row r="24" spans="1:7" ht="20">
       <c r="A24" s="13" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.5">
+    <row r="25" spans="1:7" ht="17">
       <c r="A25" s="14" t="s">
         <v>20</v>
       </c>
@@ -70671,7 +70573,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="16.5">
+    <row r="26" spans="1:7" ht="17">
       <c r="A26" s="14" t="s">
         <v>5</v>
       </c>
@@ -70694,12 +70596,12 @@
         <v>178</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="20.100000000000001">
+    <row r="28" spans="1:7" ht="20">
       <c r="A28" s="13" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="16.5">
+    <row r="29" spans="1:7" ht="17">
       <c r="A29" s="14" t="s">
         <v>20</v>
       </c>
@@ -70722,7 +70624,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="16.5">
+    <row r="30" spans="1:7" ht="17">
       <c r="A30" s="14" t="s">
         <v>6</v>
       </c>
@@ -70750,12 +70652,12 @@
         <v>28</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="20.100000000000001">
+    <row r="34" spans="1:8" ht="20">
       <c r="A34" s="13" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="17.100000000000001">
+    <row r="35" spans="1:8" ht="17">
       <c r="A35" s="14" t="s">
         <v>30</v>
       </c>
@@ -70767,7 +70669,7 @@
       <c r="E35" s="14"/>
       <c r="F35" s="14"/>
     </row>
-    <row r="36" spans="1:8" ht="17.100000000000001">
+    <row r="36" spans="1:8" ht="17">
       <c r="A36" s="14">
         <v>7</v>
       </c>
@@ -70779,7 +70681,7 @@
       <c r="E36" s="14"/>
       <c r="F36" s="14"/>
     </row>
-    <row r="38" spans="1:8" ht="32.1">
+    <row r="38" spans="1:8" ht="32">
       <c r="A38" s="1" t="s">
         <v>0</v>
       </c>
@@ -71265,7 +71167,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="61" spans="1:7" ht="32.1">
+    <row r="61" spans="1:7" ht="32">
       <c r="A61" s="1" t="s">
         <v>0</v>
       </c>
@@ -71730,12 +71632,12 @@
         <v>28</v>
       </c>
     </row>
-    <row r="83" spans="1:7" ht="20.100000000000001">
+    <row r="83" spans="1:7" ht="20">
       <c r="A83" s="13" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="84" spans="1:7" ht="17.100000000000001">
+    <row r="84" spans="1:7" ht="17">
       <c r="A84" s="14" t="s">
         <v>30</v>
       </c>
@@ -71747,7 +71649,7 @@
       <c r="E84" s="14"/>
       <c r="F84" s="14"/>
     </row>
-    <row r="85" spans="1:7" ht="17.100000000000001">
+    <row r="85" spans="1:7" ht="17">
       <c r="A85" s="14">
         <v>12</v>
       </c>
@@ -71759,7 +71661,7 @@
       <c r="E85" s="14"/>
       <c r="F85" s="14"/>
     </row>
-    <row r="87" spans="1:7" ht="32.1">
+    <row r="87" spans="1:7" ht="32">
       <c r="A87" s="1" t="s">
         <v>0</v>
       </c>
@@ -72222,7 +72124,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="109" spans="1:8" ht="32.1">
+    <row r="109" spans="1:8" ht="32">
       <c r="A109" s="1" t="s">
         <v>0</v>
       </c>
@@ -72672,7 +72574,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="132" spans="1:4" ht="20.100000000000001">
+    <row r="132" spans="1:4" ht="20">
       <c r="A132" s="10" t="s">
         <v>33</v>
       </c>
@@ -72680,7 +72582,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="133" spans="1:4" ht="20.100000000000001">
+    <row r="133" spans="1:4" ht="20">
       <c r="A133" s="33">
         <v>18</v>
       </c>
@@ -72688,7 +72590,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="134" spans="1:4" ht="20.100000000000001">
+    <row r="134" spans="1:4" ht="20">
       <c r="A134" s="10" t="s">
         <v>76</v>
       </c>
@@ -72696,7 +72598,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="135" spans="1:4" ht="20.100000000000001">
+    <row r="135" spans="1:4" ht="20">
       <c r="A135" s="10">
         <v>1</v>
       </c>
@@ -72704,7 +72606,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="1:4" ht="20.100000000000001">
+    <row r="136" spans="1:4" ht="20">
       <c r="A136" s="10" t="s">
         <v>34</v>
       </c>
@@ -72712,7 +72614,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="137" spans="1:4" ht="20.100000000000001">
+    <row r="137" spans="1:4" ht="20">
       <c r="A137" s="10" t="s">
         <v>0</v>
       </c>
@@ -72720,48 +72622,37 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="1:4" ht="15.75"/>
-    <row r="142" spans="1:4" ht="15.75"/>
-    <row r="143" spans="1:4" ht="15.75"/>
-    <row r="144" spans="1:4" ht="15.75"/>
-    <row r="145" spans="1:1" ht="15.75"/>
-    <row r="147" spans="1:1" ht="15.75"/>
-    <row r="148" spans="1:1" ht="15.75"/>
-    <row r="149" spans="1:1" ht="15.75"/>
-    <row r="150" spans="1:1" ht="15.75"/>
-    <row r="152" spans="1:1" ht="15.75"/>
-    <row r="153" spans="1:1" ht="20.25">
+    <row r="153" spans="1:1" ht="20">
       <c r="A153" s="13" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="154" spans="1:1" ht="16.5">
+    <row r="154" spans="1:1" ht="17">
       <c r="A154" s="14" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="155" spans="1:1" ht="16.5">
+    <row r="155" spans="1:1" ht="17">
       <c r="A155" s="15">
         <v>0.78779999999999994</v>
       </c>
     </row>
-    <row r="157" spans="1:1" ht="20.25">
+    <row r="157" spans="1:1" ht="20">
       <c r="A157" s="13" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="158" spans="1:1" ht="16.5">
+    <row r="158" spans="1:1" ht="17">
       <c r="A158" s="14" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="159" spans="1:1" ht="15.75"/>
     <row r="161" spans="1:11">
       <c r="A161" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="162" spans="1:11" ht="32.1">
+    <row r="162" spans="1:11" ht="32">
       <c r="A162" s="1" t="s">
         <v>0</v>
       </c>
@@ -73699,11 +73590,6 @@
         <v>74</v>
       </c>
     </row>
-    <row r="209" ht="15.75"/>
-    <row r="227" ht="15.75"/>
-    <row r="234" ht="15.75"/>
-    <row r="238" ht="15.75"/>
-    <row r="242" ht="15.75"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -73712,10 +73598,10 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{582CC3E8-7699-7A42-A102-FEB0AF971C97}">
-  <dimension ref="A1:K751"/>
-  <sheetFormatPr defaultColWidth="10.625" defaultRowHeight="15.95"/>
+  <dimension ref="A1:K720"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.58203125" defaultRowHeight="16"/>
   <sheetData>
-    <row r="1" spans="1:7" ht="32.1">
+    <row r="1" spans="1:7" ht="32">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -74893,12 +74779,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="54" spans="1:7" ht="20.25">
+    <row r="54" spans="1:7" ht="20">
       <c r="A54" s="13" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="55" spans="1:7" ht="16.5">
+    <row r="55" spans="1:7" ht="17">
       <c r="A55" s="14" t="s">
         <v>20</v>
       </c>
@@ -74921,7 +74807,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="56" spans="1:7" ht="16.5">
+    <row r="56" spans="1:7" ht="17">
       <c r="A56" s="14" t="s">
         <v>5</v>
       </c>
@@ -74944,13 +74830,12 @@
         <v>849</v>
       </c>
     </row>
-    <row r="57" spans="1:7" ht="15.75"/>
-    <row r="58" spans="1:7" ht="20.25">
+    <row r="58" spans="1:7" ht="20">
       <c r="A58" s="13" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="59" spans="1:7" ht="16.5">
+    <row r="59" spans="1:7" ht="17">
       <c r="A59" s="14" t="s">
         <v>20</v>
       </c>
@@ -74973,7 +74858,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="60" spans="1:7" ht="16.5">
+    <row r="60" spans="1:7" ht="17">
       <c r="A60" s="14" t="s">
         <v>6</v>
       </c>
@@ -75001,12 +74886,12 @@
         <v>81</v>
       </c>
     </row>
-    <row r="63" spans="1:7" ht="20.100000000000001">
+    <row r="63" spans="1:7" ht="20">
       <c r="A63" s="13" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="64" spans="1:7" ht="17.100000000000001">
+    <row r="64" spans="1:7" ht="17">
       <c r="A64" s="14" t="s">
         <v>30</v>
       </c>
@@ -75019,7 +74904,7 @@
       <c r="F64" s="14"/>
       <c r="G64" s="14"/>
     </row>
-    <row r="65" spans="1:7" ht="17.100000000000001">
+    <row r="65" spans="1:7" ht="17">
       <c r="A65" s="14">
         <v>24</v>
       </c>
@@ -75032,7 +74917,7 @@
       <c r="F65" s="14"/>
       <c r="G65" s="14"/>
     </row>
-    <row r="66" spans="1:7" ht="17.100000000000001">
+    <row r="66" spans="1:7" ht="17">
       <c r="A66" s="14">
         <v>32</v>
       </c>
@@ -75045,7 +74930,7 @@
       <c r="F66" s="14"/>
       <c r="G66" s="14"/>
     </row>
-    <row r="67" spans="1:7" ht="17.100000000000001">
+    <row r="67" spans="1:7" ht="17">
       <c r="A67" s="14">
         <v>43</v>
       </c>
@@ -75058,7 +74943,7 @@
       <c r="F67" s="14"/>
       <c r="G67" s="14"/>
     </row>
-    <row r="68" spans="1:7" ht="17.100000000000001">
+    <row r="68" spans="1:7" ht="17">
       <c r="A68" s="14">
         <v>48</v>
       </c>
@@ -75071,7 +74956,7 @@
       <c r="F68" s="14"/>
       <c r="G68" s="14"/>
     </row>
-    <row r="69" spans="1:7" ht="17.100000000000001">
+    <row r="69" spans="1:7" ht="17">
       <c r="A69" s="14">
         <v>50</v>
       </c>
@@ -75084,10 +74969,10 @@
       <c r="F69" s="14"/>
       <c r="G69" s="14"/>
     </row>
-    <row r="70" spans="1:7" ht="17.100000000000001">
+    <row r="70" spans="1:7" ht="17">
       <c r="A70" s="16"/>
     </row>
-    <row r="71" spans="1:7" ht="32.1">
+    <row r="71" spans="1:7" ht="32">
       <c r="A71" s="1" t="s">
         <v>0</v>
       </c>
@@ -76275,7 +76160,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="124" spans="1:8" ht="32.1">
+    <row r="124" spans="1:8" ht="32">
       <c r="A124" s="1" t="s">
         <v>0</v>
       </c>
@@ -77338,12 +77223,12 @@
         <v>28</v>
       </c>
     </row>
-    <row r="172" spans="1:7" ht="20.100000000000001">
+    <row r="172" spans="1:7" ht="20">
       <c r="A172" s="13" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="173" spans="1:7" ht="17.100000000000001">
+    <row r="173" spans="1:7" ht="17">
       <c r="A173" s="14" t="s">
         <v>30</v>
       </c>
@@ -77356,7 +77241,7 @@
       <c r="F173" s="14"/>
       <c r="G173" s="14"/>
     </row>
-    <row r="174" spans="1:7" ht="17.100000000000001">
+    <row r="174" spans="1:7" ht="17">
       <c r="A174" s="14">
         <v>25</v>
       </c>
@@ -77369,7 +77254,7 @@
       <c r="F174" s="14"/>
       <c r="G174" s="14"/>
     </row>
-    <row r="175" spans="1:7" ht="17.100000000000001">
+    <row r="175" spans="1:7" ht="17">
       <c r="A175" s="14">
         <v>45</v>
       </c>
@@ -77382,7 +77267,7 @@
       <c r="F175" s="14"/>
       <c r="G175" s="14"/>
     </row>
-    <row r="177" spans="1:7" ht="32.1">
+    <row r="177" spans="1:7" ht="32">
       <c r="A177" s="1" t="s">
         <v>0</v>
       </c>
@@ -78446,7 +78331,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="225" spans="1:7" ht="32.1">
+    <row r="225" spans="1:7" ht="32">
       <c r="A225" s="1" t="s">
         <v>0</v>
       </c>
@@ -79463,12 +79348,12 @@
         <v>28</v>
       </c>
     </row>
-    <row r="272" spans="1:7" ht="20.100000000000001">
+    <row r="272" spans="1:7" ht="20">
       <c r="A272" s="13" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="273" spans="1:7" ht="17.100000000000001">
+    <row r="273" spans="1:7" ht="17">
       <c r="A273" s="14" t="s">
         <v>30</v>
       </c>
@@ -79480,7 +79365,7 @@
       <c r="E273" s="14"/>
       <c r="F273" s="14"/>
     </row>
-    <row r="274" spans="1:7" ht="17.100000000000001">
+    <row r="274" spans="1:7" ht="17">
       <c r="A274" s="14">
         <v>41</v>
       </c>
@@ -79492,7 +79377,7 @@
       <c r="E274" s="14"/>
       <c r="F274" s="14"/>
     </row>
-    <row r="275" spans="1:7" ht="17.100000000000001">
+    <row r="275" spans="1:7" ht="17">
       <c r="A275" s="14">
         <v>43</v>
       </c>
@@ -79504,7 +79389,7 @@
       <c r="E275" s="14"/>
       <c r="F275" s="14"/>
     </row>
-    <row r="277" spans="1:7" ht="32.1">
+    <row r="277" spans="1:7" ht="32">
       <c r="A277" s="1" t="s">
         <v>0</v>
       </c>
@@ -80522,7 +80407,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="323" spans="1:7" ht="32.1">
+    <row r="323" spans="1:7" ht="32">
       <c r="A323" s="1" t="s">
         <v>0</v>
       </c>
@@ -81488,17 +81373,17 @@
         <v>734</v>
       </c>
     </row>
-    <row r="366" spans="1:7" ht="15.75">
+    <row r="366" spans="1:7">
       <c r="A366" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="367" spans="1:7" ht="20.100000000000001">
+    <row r="367" spans="1:7" ht="20">
       <c r="A367" s="13" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="368" spans="1:7" ht="17.100000000000001">
+    <row r="368" spans="1:7" ht="17">
       <c r="A368" s="14" t="s">
         <v>30</v>
       </c>
@@ -81511,7 +81396,7 @@
       <c r="F368" s="14"/>
       <c r="G368" s="14"/>
     </row>
-    <row r="369" spans="1:7" ht="17.100000000000001">
+    <row r="369" spans="1:7" ht="17">
       <c r="A369" s="14">
         <v>13</v>
       </c>
@@ -81524,7 +81409,7 @@
       <c r="F369" s="14"/>
       <c r="G369" s="14"/>
     </row>
-    <row r="370" spans="1:7" ht="17.100000000000001">
+    <row r="370" spans="1:7" ht="17">
       <c r="A370" s="14">
         <v>32</v>
       </c>
@@ -81537,7 +81422,7 @@
       <c r="F370" s="14"/>
       <c r="G370" s="14"/>
     </row>
-    <row r="371" spans="1:7" ht="17.100000000000001">
+    <row r="371" spans="1:7" ht="17">
       <c r="A371" s="14">
         <v>40</v>
       </c>
@@ -81550,7 +81435,7 @@
       <c r="F371" s="14"/>
       <c r="G371" s="14"/>
     </row>
-    <row r="372" spans="1:7" ht="17.100000000000001">
+    <row r="372" spans="1:7" ht="17">
       <c r="A372" s="14">
         <v>41</v>
       </c>
@@ -81563,7 +81448,7 @@
       <c r="F372" s="14"/>
       <c r="G372" s="14"/>
     </row>
-    <row r="374" spans="1:7" ht="32.1">
+    <row r="374" spans="1:7" ht="32">
       <c r="A374" s="1" t="s">
         <v>0</v>
       </c>
@@ -82541,7 +82426,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="418" spans="1:7" ht="32.1">
+    <row r="418" spans="1:7" ht="32">
       <c r="A418" s="1" t="s">
         <v>0</v>
       </c>
@@ -83420,12 +83305,12 @@
         <v>28</v>
       </c>
     </row>
-    <row r="459" spans="1:7" ht="20.100000000000001">
+    <row r="459" spans="1:7" ht="20">
       <c r="A459" s="13" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="460" spans="1:7" ht="17.100000000000001">
+    <row r="460" spans="1:7" ht="17">
       <c r="A460" s="14" t="s">
         <v>30</v>
       </c>
@@ -83437,7 +83322,7 @@
       <c r="E460" s="14"/>
       <c r="F460" s="14"/>
     </row>
-    <row r="461" spans="1:7" ht="17.100000000000001">
+    <row r="461" spans="1:7" ht="17">
       <c r="A461" s="14">
         <v>12</v>
       </c>
@@ -83449,7 +83334,7 @@
       <c r="E461" s="14"/>
       <c r="F461" s="14"/>
     </row>
-    <row r="462" spans="1:7" ht="17.100000000000001">
+    <row r="462" spans="1:7" ht="17">
       <c r="A462" s="14">
         <v>19</v>
       </c>
@@ -83461,10 +83346,10 @@
       <c r="E462" s="14"/>
       <c r="F462" s="14"/>
     </row>
-    <row r="463" spans="1:7" ht="17.100000000000001">
+    <row r="463" spans="1:7" ht="17">
       <c r="A463" s="16"/>
     </row>
-    <row r="465" spans="1:8" ht="32.1">
+    <row r="465" spans="1:8" ht="32">
       <c r="A465" s="1" t="s">
         <v>0</v>
       </c>
@@ -84344,7 +84229,7 @@
         <v>1305</v>
       </c>
     </row>
-    <row r="505" spans="1:7" ht="32.1">
+    <row r="505" spans="1:7" ht="32">
       <c r="A505" s="1" t="s">
         <v>0</v>
       </c>
@@ -85177,12 +85062,12 @@
         <v>28</v>
       </c>
     </row>
-    <row r="544" spans="1:7" ht="20.100000000000001">
+    <row r="544" spans="1:7" ht="20">
       <c r="A544" s="13" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="545" spans="1:7" ht="17.100000000000001">
+    <row r="545" spans="1:7" ht="17">
       <c r="A545" s="14" t="s">
         <v>30</v>
       </c>
@@ -85194,7 +85079,7 @@
       <c r="E545" s="14"/>
       <c r="F545" s="14"/>
     </row>
-    <row r="546" spans="1:7" ht="17.100000000000001">
+    <row r="546" spans="1:7" ht="17">
       <c r="A546" s="14">
         <v>23</v>
       </c>
@@ -85206,10 +85091,10 @@
       <c r="E546" s="14"/>
       <c r="F546" s="14"/>
     </row>
-    <row r="547" spans="1:7" ht="17.100000000000001">
+    <row r="547" spans="1:7" ht="17">
       <c r="A547" s="16"/>
     </row>
-    <row r="549" spans="1:7" ht="32.1">
+    <row r="549" spans="1:7" ht="32">
       <c r="A549" s="1" t="s">
         <v>0</v>
       </c>
@@ -86040,7 +85925,7 @@
         <v>1305</v>
       </c>
     </row>
-    <row r="587" spans="1:7" ht="32.1">
+    <row r="587" spans="1:7" ht="32">
       <c r="A587" s="1" t="s">
         <v>0</v>
       </c>
@@ -86858,7 +86743,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="626" spans="1:4" ht="20.100000000000001">
+    <row r="626" spans="1:4" ht="20">
       <c r="A626" s="10" t="s">
         <v>33</v>
       </c>
@@ -86866,7 +86751,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="627" spans="1:4" ht="20.100000000000001">
+    <row r="627" spans="1:4" ht="20">
       <c r="A627" s="33">
         <v>34</v>
       </c>
@@ -86874,7 +86759,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="628" spans="1:4" ht="20.100000000000001">
+    <row r="628" spans="1:4" ht="20">
       <c r="A628" s="10" t="s">
         <v>76</v>
       </c>
@@ -86882,7 +86767,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="629" spans="1:4" ht="20.100000000000001">
+    <row r="629" spans="1:4" ht="20">
       <c r="A629" s="10">
         <v>1</v>
       </c>
@@ -86890,7 +86775,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="630" spans="1:4" ht="20.100000000000001">
+    <row r="630" spans="1:4" ht="20">
       <c r="A630" s="10" t="s">
         <v>34</v>
       </c>
@@ -86898,7 +86783,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="631" spans="1:4" ht="20.100000000000001">
+    <row r="631" spans="1:4" ht="20">
       <c r="A631" s="10" t="s">
         <v>0</v>
       </c>
@@ -86906,48 +86791,38 @@
         <v>0</v>
       </c>
     </row>
-    <row r="632" spans="1:4" ht="20.100000000000001">
+    <row r="632" spans="1:4" ht="20">
       <c r="A632" s="10"/>
       <c r="D632" s="10"/>
     </row>
-    <row r="634" spans="1:4" ht="15.75">
+    <row r="634" spans="1:4">
       <c r="A634" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="635" spans="1:4" ht="15.75"/>
-    <row r="636" spans="1:4" ht="15.75"/>
-    <row r="637" spans="1:4" ht="15.75"/>
-    <row r="638" spans="1:4" ht="15.75"/>
-    <row r="641" spans="1:2" ht="15.75"/>
-    <row r="642" spans="1:2" ht="15.75"/>
-    <row r="643" spans="1:2" ht="15.75"/>
-    <row r="646" spans="1:2" ht="15.75"/>
-    <row r="647" spans="1:2" ht="15.75"/>
-    <row r="648" spans="1:2" ht="15.75"/>
-    <row r="649" spans="1:2" ht="20.25">
+    <row r="649" spans="1:2" ht="20">
       <c r="A649" s="13" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="650" spans="1:2" ht="16.5">
+    <row r="650" spans="1:2" ht="17">
       <c r="A650" s="14" t="s">
         <v>37</v>
       </c>
       <c r="B650" s="14"/>
     </row>
-    <row r="651" spans="1:2" ht="16.5">
+    <row r="651" spans="1:2" ht="17">
       <c r="A651" s="15">
         <v>0.85219999999999996</v>
       </c>
       <c r="B651" s="15"/>
     </row>
-    <row r="653" spans="1:2" ht="20.25">
+    <row r="653" spans="1:2" ht="20">
       <c r="A653" s="13" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="654" spans="1:2" ht="16.5">
+    <row r="654" spans="1:2" ht="17">
       <c r="A654" s="14" t="s">
         <v>85</v>
       </c>
@@ -86957,7 +86832,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="658" spans="1:11" ht="32.1">
+    <row r="658" spans="1:11" ht="32">
       <c r="A658" s="1" t="s">
         <v>0</v>
       </c>
@@ -88472,7 +88347,6 @@
         <v>74</v>
       </c>
     </row>
-    <row r="751" ht="15.75"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
